--- a/data/total_edits.xlsx
+++ b/data/total_edits.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/LLopez-Jensen/Documents/GitHub/9-11-memorials/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1087DA-662B-1044-ADBF-939EE78FAFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{901EF710-D7B7-2849-87B7-6B82CECAFC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3797,7 +3797,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3805,7 +3805,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4951,7 +4950,7 @@
       <c r="G32" t="s">
         <v>741</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="H32" t="s">
         <v>250</v>
       </c>
       <c r="K32" t="s">
@@ -5962,7 +5961,7 @@
       <c r="G74" t="s">
         <v>744</v>
       </c>
-      <c r="H74" s="3" t="s">
+      <c r="H74" t="s">
         <v>275</v>
       </c>
       <c r="K74" t="s">
@@ -8011,7 +8010,7 @@
       <c r="G158" t="s">
         <v>714</v>
       </c>
-      <c r="H158" s="3" t="s">
+      <c r="H158" t="s">
         <v>1194</v>
       </c>
       <c r="K158" t="s">

--- a/data/total_edits.xlsx
+++ b/data/total_edits.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/LLopez-Jensen/Documents/GitHub/9-11-memorials/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{901EF710-D7B7-2849-87B7-6B82CECAFC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE764EE-E096-F845-A843-D0038667651D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$H$1:$H$328</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$K$1:$K$325</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1961" uniqueCount="1197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2286" uniqueCount="1208">
   <si>
     <t>new_name</t>
   </si>
@@ -2523,9 +2523,6 @@
   </si>
   <si>
     <t>https://voicescenter.org/living-memorial/memorials/fordham-university-gym-seat</t>
-  </si>
-  <si>
-    <t>Fort Greene Park Groove of Trees</t>
   </si>
   <si>
     <t>https://voicescenter.org/living-memorial/memorials/fort-greene-park-groove-trees</t>
@@ -3754,6 +3751,42 @@
   </si>
   <si>
     <t>council_member</t>
+  </si>
+  <si>
+    <t>land_use</t>
+  </si>
+  <si>
+    <t>Street</t>
+  </si>
+  <si>
+    <t>Intersection</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>Place of Worship</t>
+  </si>
+  <si>
+    <t>Bench</t>
+  </si>
+  <si>
+    <t>Greenspace</t>
+  </si>
+  <si>
+    <t>Bar/Restaurant</t>
+  </si>
+  <si>
+    <t>Plaque/Wall</t>
+  </si>
+  <si>
+    <t>Artwork/Exhibition</t>
+  </si>
+  <si>
+    <t>University/Library</t>
+  </si>
+  <si>
+    <t>Fort Greene Park Grove of Trees</t>
   </si>
 </sst>
 </file>
@@ -4109,7 +4142,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K325"/>
+  <dimension ref="A1:L325"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.83203125" customWidth="1"/>
@@ -4119,7 +4152,7 @@
     <col min="5" max="10" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4142,24 +4175,27 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+        <v>997</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>718</v>
       </c>
       <c r="B2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C2" t="s">
         <v>719</v>
@@ -4177,13 +4213,16 @@
         <v>720</v>
       </c>
       <c r="H2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="K2" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>602</v>
       </c>
@@ -4209,10 +4248,13 @@
         <v>606</v>
       </c>
       <c r="K3" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L3" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>153</v>
       </c>
@@ -4235,10 +4277,13 @@
         <v>156</v>
       </c>
       <c r="K4" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>261</v>
       </c>
@@ -4261,15 +4306,18 @@
         <v>174</v>
       </c>
       <c r="K5" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L5" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>821</v>
       </c>
       <c r="B6" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D6" t="s">
         <v>71</v>
@@ -4281,18 +4329,21 @@
         <v>822</v>
       </c>
       <c r="K6" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L6" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C7" t="s">
         <v>1038</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1120</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1039</v>
       </c>
       <c r="D7" t="s">
         <v>37</v>
@@ -4307,18 +4358,21 @@
         <v>185</v>
       </c>
       <c r="K7" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L7" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C8" t="s">
         <v>1040</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1041</v>
       </c>
       <c r="D8" t="s">
         <v>37</v>
@@ -4333,18 +4387,21 @@
         <v>185</v>
       </c>
       <c r="K8" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L8" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C9" t="s">
         <v>1015</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1070</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1016</v>
       </c>
       <c r="D9" t="s">
         <v>37</v>
@@ -4359,18 +4416,21 @@
         <v>185</v>
       </c>
       <c r="K9" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L9" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C10" t="s">
         <v>1003</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1004</v>
       </c>
       <c r="D10" t="s">
         <v>37</v>
@@ -4385,18 +4445,21 @@
         <v>185</v>
       </c>
       <c r="K10" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L10" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C11" t="s">
         <v>1017</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1018</v>
       </c>
       <c r="D11" t="s">
         <v>37</v>
@@ -4411,18 +4474,21 @@
         <v>185</v>
       </c>
       <c r="K11" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L11" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C12" t="s">
         <v>1032</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1033</v>
       </c>
       <c r="D12" t="s">
         <v>37</v>
@@ -4437,10 +4503,13 @@
         <v>185</v>
       </c>
       <c r="K12" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L12" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>607</v>
       </c>
@@ -4466,10 +4535,13 @@
         <v>611</v>
       </c>
       <c r="K13" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L13" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>212</v>
       </c>
@@ -4492,10 +4564,13 @@
         <v>215</v>
       </c>
       <c r="K14" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L14" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>490</v>
       </c>
@@ -4521,18 +4596,21 @@
         <v>494</v>
       </c>
       <c r="K15" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L15" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C16" t="s">
         <v>1005</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1006</v>
       </c>
       <c r="D16" t="s">
         <v>37</v>
@@ -4547,18 +4625,21 @@
         <v>185</v>
       </c>
       <c r="K16" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L16" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C17" t="s">
         <v>1007</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1063</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1008</v>
       </c>
       <c r="D17" t="s">
         <v>37</v>
@@ -4573,18 +4654,21 @@
         <v>185</v>
       </c>
       <c r="K17" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L17" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C18" t="s">
         <v>1024</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1025</v>
       </c>
       <c r="D18" t="s">
         <v>37</v>
@@ -4599,18 +4683,21 @@
         <v>185</v>
       </c>
       <c r="K18" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L18" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C19" t="s">
         <v>1036</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1037</v>
       </c>
       <c r="D19" t="s">
         <v>37</v>
@@ -4625,18 +4712,21 @@
         <v>185</v>
       </c>
       <c r="K19" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L19" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C20" t="s">
         <v>1009</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1010</v>
       </c>
       <c r="D20" t="s">
         <v>37</v>
@@ -4651,18 +4741,21 @@
         <v>185</v>
       </c>
       <c r="K20" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L20" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C21" t="s">
         <v>1013</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1014</v>
       </c>
       <c r="D21" t="s">
         <v>37</v>
@@ -4677,18 +4770,21 @@
         <v>185</v>
       </c>
       <c r="K21" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L21" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C22" t="s">
         <v>1028</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1029</v>
       </c>
       <c r="D22" t="s">
         <v>37</v>
@@ -4703,18 +4799,21 @@
         <v>185</v>
       </c>
       <c r="K22" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L22" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C23" t="s">
         <v>1019</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1020</v>
       </c>
       <c r="D23" t="s">
         <v>37</v>
@@ -4729,18 +4828,21 @@
         <v>185</v>
       </c>
       <c r="K23" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L23" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C24" t="s">
         <v>1034</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1117</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1035</v>
       </c>
       <c r="D24" t="s">
         <v>37</v>
@@ -4755,15 +4857,18 @@
         <v>185</v>
       </c>
       <c r="K24" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L24" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>671</v>
       </c>
       <c r="B25" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C25" t="s">
         <v>672</v>
@@ -4781,10 +4886,13 @@
         <v>185</v>
       </c>
       <c r="K25" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L25" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>519</v>
       </c>
@@ -4810,18 +4918,21 @@
         <v>185</v>
       </c>
       <c r="K26" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L26" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C27" t="s">
         <v>1026</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1079</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1027</v>
       </c>
       <c r="D27" t="s">
         <v>37</v>
@@ -4836,15 +4947,18 @@
         <v>185</v>
       </c>
       <c r="K27" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L27" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B28" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="D28" t="s">
         <v>37</v>
@@ -4853,18 +4967,21 @@
         <v>11209</v>
       </c>
       <c r="I28" t="s">
+        <v>907</v>
+      </c>
+      <c r="K28" t="s">
+        <v>1181</v>
+      </c>
+      <c r="L28" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>908</v>
       </c>
-      <c r="K28" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>909</v>
-      </c>
       <c r="B29" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="D29" t="s">
         <v>37</v>
@@ -4873,18 +4990,21 @@
         <v>11230</v>
       </c>
       <c r="I29" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="K29" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L29" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B30" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="D30" t="s">
         <v>37</v>
@@ -4893,18 +5013,21 @@
         <v>11232</v>
       </c>
       <c r="I30" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="K30" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L30" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>700</v>
       </c>
       <c r="B31" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C31" t="s">
         <v>701</v>
@@ -4922,18 +5045,21 @@
         <v>702</v>
       </c>
       <c r="H31" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K31" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L31" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>739</v>
       </c>
       <c r="B32" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C32" t="s">
         <v>740</v>
@@ -4954,10 +5080,13 @@
         <v>250</v>
       </c>
       <c r="K32" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L32" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>231</v>
       </c>
@@ -4980,10 +5109,13 @@
         <v>234</v>
       </c>
       <c r="K33" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L33" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>235</v>
       </c>
@@ -5006,15 +5138,18 @@
         <v>234</v>
       </c>
       <c r="K34" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L34" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B35" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="D35" t="s">
         <v>111</v>
@@ -5023,18 +5158,21 @@
         <v>10001</v>
       </c>
       <c r="I35" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="K35" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L35" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B36" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D36" t="s">
         <v>111</v>
@@ -5043,18 +5181,21 @@
         <v>10002</v>
       </c>
       <c r="I36" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="K36" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L36" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>779</v>
       </c>
       <c r="B37" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="D37" t="s">
         <v>111</v>
@@ -5069,15 +5210,18 @@
         <v>781</v>
       </c>
       <c r="K37" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L37" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B38" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D38" t="s">
         <v>111</v>
@@ -5086,18 +5230,21 @@
         <v>10003</v>
       </c>
       <c r="I38" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="K38" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L38" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>797</v>
       </c>
       <c r="B39" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="D39" t="s">
         <v>111</v>
@@ -5109,15 +5256,18 @@
         <v>798</v>
       </c>
       <c r="K39" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L39" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B40" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D40" t="s">
         <v>111</v>
@@ -5126,18 +5276,21 @@
         <v>10012</v>
       </c>
       <c r="I40" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="K40" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L40" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>793</v>
       </c>
       <c r="B41" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="D41" t="s">
         <v>111</v>
@@ -5149,15 +5302,18 @@
         <v>794</v>
       </c>
       <c r="K41" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L41" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B42" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D42" t="s">
         <v>111</v>
@@ -5166,18 +5322,21 @@
         <v>10022</v>
       </c>
       <c r="I42" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K42" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L42" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B43" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="D43" t="s">
         <v>111</v>
@@ -5186,18 +5345,21 @@
         <v>10022</v>
       </c>
       <c r="I43" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="K43" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L43" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>764</v>
       </c>
       <c r="B44" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="D44" t="s">
         <v>111</v>
@@ -5212,15 +5374,18 @@
         <v>766</v>
       </c>
       <c r="K44" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L44" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B45" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="D45" t="s">
         <v>111</v>
@@ -5229,18 +5394,21 @@
         <v>10023</v>
       </c>
       <c r="I45" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="K45" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L45" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B46" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D46" t="s">
         <v>111</v>
@@ -5249,18 +5417,21 @@
         <v>10024</v>
       </c>
       <c r="I46" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="K46" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L46" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B47" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="D47" t="s">
         <v>111</v>
@@ -5269,18 +5440,21 @@
         <v>10024</v>
       </c>
       <c r="I47" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="K47" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L47" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B48" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="D48" t="s">
         <v>111</v>
@@ -5289,18 +5463,21 @@
         <v>10024</v>
       </c>
       <c r="I48" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="K48" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L48" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B49" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="D49" t="s">
         <v>111</v>
@@ -5309,21 +5486,24 @@
         <v>10036</v>
       </c>
       <c r="I49" t="s">
+        <v>881</v>
+      </c>
+      <c r="J49" t="s">
         <v>882</v>
       </c>
-      <c r="J49" t="s">
-        <v>883</v>
-      </c>
       <c r="K49" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L49" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>805</v>
       </c>
       <c r="B50" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="D50" t="s">
         <v>111</v>
@@ -5335,15 +5515,18 @@
         <v>806</v>
       </c>
       <c r="K50" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L50" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>860</v>
+      </c>
+      <c r="B51" t="s">
         <v>861</v>
-      </c>
-      <c r="B51" t="s">
-        <v>862</v>
       </c>
       <c r="D51" t="s">
         <v>111</v>
@@ -5352,18 +5535,21 @@
         <v>10065</v>
       </c>
       <c r="I51" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K51" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L51" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B52" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="D52" t="s">
         <v>111</v>
@@ -5372,18 +5558,21 @@
         <v>10128</v>
       </c>
       <c r="I52" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="K52" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L52" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>736</v>
       </c>
       <c r="B53" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C53" t="s">
         <v>737</v>
@@ -5404,15 +5593,18 @@
         <v>260</v>
       </c>
       <c r="K53" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L53" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>727</v>
       </c>
       <c r="B54" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C54" t="s">
         <v>728</v>
@@ -5430,18 +5622,21 @@
         <v>729</v>
       </c>
       <c r="H54" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="K54" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L54" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>733</v>
       </c>
       <c r="B55" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C55" t="s">
         <v>734</v>
@@ -5462,15 +5657,18 @@
         <v>260</v>
       </c>
       <c r="K55" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L55" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>724</v>
       </c>
       <c r="B56" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C56" t="s">
         <v>725</v>
@@ -5488,13 +5686,16 @@
         <v>726</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="K56" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L56" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>257</v>
       </c>
@@ -5517,10 +5718,13 @@
         <v>260</v>
       </c>
       <c r="K57" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L57" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>545</v>
       </c>
@@ -5546,10 +5750,13 @@
         <v>549</v>
       </c>
       <c r="K58" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L58" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>612</v>
       </c>
@@ -5575,10 +5782,13 @@
         <v>616</v>
       </c>
       <c r="K59" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L59" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>586</v>
       </c>
@@ -5601,13 +5811,16 @@
         <v>589</v>
       </c>
       <c r="H60" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="K60" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L60" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>346</v>
       </c>
@@ -5630,10 +5843,13 @@
         <v>345</v>
       </c>
       <c r="K61" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L61" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>342</v>
       </c>
@@ -5656,15 +5872,18 @@
         <v>345</v>
       </c>
       <c r="K62" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L62" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B63" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
@@ -5673,18 +5892,21 @@
         <v>11362</v>
       </c>
       <c r="I63" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K63" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L63" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B64" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
@@ -5693,18 +5915,21 @@
         <v>11362</v>
       </c>
       <c r="I64" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="K64" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L64" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>762</v>
       </c>
       <c r="B65" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
@@ -5716,15 +5941,18 @@
         <v>763</v>
       </c>
       <c r="K65" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L65" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>784</v>
       </c>
       <c r="B66" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="D66" t="s">
         <v>11</v>
@@ -5736,18 +5964,21 @@
         <v>785</v>
       </c>
       <c r="K66" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L66" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B67" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C67" t="s">
         <v>1115</v>
-      </c>
-      <c r="C67" t="s">
-        <v>1116</v>
       </c>
       <c r="D67" t="s">
         <v>16</v>
@@ -5762,18 +5993,21 @@
         <v>223</v>
       </c>
       <c r="I67" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="K67" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L67" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>657</v>
       </c>
       <c r="B68" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C68" t="s">
         <v>658</v>
@@ -5791,15 +6025,18 @@
         <v>170</v>
       </c>
       <c r="K68" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L68" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>703</v>
       </c>
       <c r="B69" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C69" t="s">
         <v>704</v>
@@ -5820,15 +6057,18 @@
         <v>170</v>
       </c>
       <c r="K69" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L69" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>697</v>
       </c>
       <c r="B70" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C70" t="s">
         <v>698</v>
@@ -5849,15 +6089,18 @@
         <v>275</v>
       </c>
       <c r="K70" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L70" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>691</v>
       </c>
       <c r="B71" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C71" t="s">
         <v>692</v>
@@ -5878,15 +6121,18 @@
         <v>275</v>
       </c>
       <c r="K71" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L71" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>694</v>
       </c>
       <c r="B72" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C72" t="s">
         <v>695</v>
@@ -5907,15 +6153,18 @@
         <v>275</v>
       </c>
       <c r="K72" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L72" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>709</v>
       </c>
       <c r="B73" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C73" t="s">
         <v>710</v>
@@ -5936,15 +6185,18 @@
         <v>275</v>
       </c>
       <c r="K73" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L73" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>742</v>
       </c>
       <c r="B74" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C74" t="s">
         <v>743</v>
@@ -5965,10 +6217,13 @@
         <v>275</v>
       </c>
       <c r="K74" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L74" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>73</v>
       </c>
@@ -5991,15 +6246,18 @@
         <v>76</v>
       </c>
       <c r="K75" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L75" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>651</v>
       </c>
       <c r="B76" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C76" t="s">
         <v>652</v>
@@ -6017,10 +6275,13 @@
         <v>170</v>
       </c>
       <c r="K76" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L76" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>205</v>
       </c>
@@ -6043,10 +6304,13 @@
         <v>170</v>
       </c>
       <c r="K77" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L77" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>673</v>
       </c>
@@ -6069,15 +6333,18 @@
         <v>83</v>
       </c>
       <c r="K78" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L78" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>795</v>
       </c>
       <c r="B79" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="D79" t="s">
         <v>16</v>
@@ -6089,15 +6356,18 @@
         <v>796</v>
       </c>
       <c r="K79" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L79" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B80" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="D80" t="s">
         <v>16</v>
@@ -6106,18 +6376,21 @@
         <v>10301</v>
       </c>
       <c r="I80" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="K80" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L80" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>755</v>
       </c>
       <c r="B81" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D81" t="s">
         <v>16</v>
@@ -6129,15 +6402,18 @@
         <v>756</v>
       </c>
       <c r="K81" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L81" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B82" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="D82" t="s">
         <v>16</v>
@@ -6146,18 +6422,21 @@
         <v>10305</v>
       </c>
       <c r="I82" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="K82" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L82" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B83" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D83" t="s">
         <v>16</v>
@@ -6166,18 +6445,21 @@
         <v>10312</v>
       </c>
       <c r="I83" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="K83" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1181</v>
+      </c>
+      <c r="L83" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>819</v>
       </c>
       <c r="B84" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="D84" t="s">
         <v>71</v>
@@ -6189,15 +6471,18 @@
         <v>820</v>
       </c>
       <c r="K84" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L84" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
+        <v>976</v>
+      </c>
+      <c r="B85" t="s">
         <v>977</v>
-      </c>
-      <c r="B85" t="s">
-        <v>978</v>
       </c>
       <c r="D85" t="s">
         <v>71</v>
@@ -6206,21 +6491,24 @@
         <v>10460</v>
       </c>
       <c r="I85" t="s">
+        <v>978</v>
+      </c>
+      <c r="J85" t="s">
         <v>979</v>
       </c>
-      <c r="J85" t="s">
-        <v>980</v>
-      </c>
       <c r="K85" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L85" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B86" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D86" t="s">
         <v>71</v>
@@ -6229,13 +6517,16 @@
         <v>10468</v>
       </c>
       <c r="I86" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="K86" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L86" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>414</v>
       </c>
@@ -6255,13 +6546,16 @@
         <v>2017</v>
       </c>
       <c r="H87" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="K87" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L87" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>227</v>
       </c>
@@ -6284,15 +6578,18 @@
         <v>230</v>
       </c>
       <c r="K88" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L88" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B89" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="D89" t="s">
         <v>37</v>
@@ -6301,18 +6598,21 @@
         <v>11209</v>
       </c>
       <c r="I89" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="K89" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L89" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B90" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="D90" t="s">
         <v>37</v>
@@ -6321,18 +6621,21 @@
         <v>11220</v>
       </c>
       <c r="I90" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="K90" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L90" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
+        <v>980</v>
+      </c>
+      <c r="B91" t="s">
         <v>981</v>
-      </c>
-      <c r="B91" t="s">
-        <v>982</v>
       </c>
       <c r="D91" t="s">
         <v>37</v>
@@ -6341,16 +6644,19 @@
         <v>11221</v>
       </c>
       <c r="I91" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="J91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="K91" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L91" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>757</v>
       </c>
@@ -6367,15 +6673,18 @@
         <v>759</v>
       </c>
       <c r="K92" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L92" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
+        <v>946</v>
+      </c>
+      <c r="B93" t="s">
         <v>947</v>
-      </c>
-      <c r="B93" t="s">
-        <v>948</v>
       </c>
       <c r="D93" t="s">
         <v>37</v>
@@ -6384,18 +6693,21 @@
         <v>11224</v>
       </c>
       <c r="I93" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="K93" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L93" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
+        <v>942</v>
+      </c>
+      <c r="B94" t="s">
         <v>943</v>
-      </c>
-      <c r="B94" t="s">
-        <v>944</v>
       </c>
       <c r="D94" t="s">
         <v>37</v>
@@ -6404,21 +6716,24 @@
         <v>11225</v>
       </c>
       <c r="I94" t="s">
+        <v>944</v>
+      </c>
+      <c r="J94" t="s">
         <v>945</v>
       </c>
-      <c r="J94" t="s">
-        <v>946</v>
-      </c>
       <c r="K94" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L94" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B95" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="D95" t="s">
         <v>37</v>
@@ -6427,21 +6742,24 @@
         <v>11228</v>
       </c>
       <c r="I95" t="s">
+        <v>950</v>
+      </c>
+      <c r="J95" t="s">
         <v>951</v>
       </c>
-      <c r="J95" t="s">
-        <v>952</v>
-      </c>
       <c r="K95" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L95" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B96" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="D96" t="s">
         <v>37</v>
@@ -6450,18 +6768,21 @@
         <v>11228</v>
       </c>
       <c r="I96" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="K96" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L96" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
+        <v>938</v>
+      </c>
+      <c r="B97" t="s">
         <v>939</v>
-      </c>
-      <c r="B97" t="s">
-        <v>940</v>
       </c>
       <c r="D97" t="s">
         <v>37</v>
@@ -6470,24 +6791,27 @@
         <v>11235</v>
       </c>
       <c r="I97" t="s">
+        <v>940</v>
+      </c>
+      <c r="J97" t="s">
         <v>941</v>
       </c>
-      <c r="J97" t="s">
-        <v>942</v>
-      </c>
       <c r="K97" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L97" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C98" t="s">
         <v>1011</v>
-      </c>
-      <c r="B98" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C98" t="s">
-        <v>1012</v>
       </c>
       <c r="D98" t="s">
         <v>111</v>
@@ -6502,10 +6826,13 @@
         <v>234</v>
       </c>
       <c r="K98" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L98" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>807</v>
       </c>
@@ -6522,15 +6849,18 @@
         <v>809</v>
       </c>
       <c r="K99" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L99" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>750</v>
       </c>
       <c r="B100" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="D100" t="s">
         <v>111</v>
@@ -6542,15 +6872,18 @@
         <v>751</v>
       </c>
       <c r="K100" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L100" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B101" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="D101" t="s">
         <v>111</v>
@@ -6559,21 +6892,24 @@
         <v>10004</v>
       </c>
       <c r="I101" t="s">
+        <v>832</v>
+      </c>
+      <c r="J101" t="s">
         <v>833</v>
       </c>
-      <c r="J101" t="s">
-        <v>834</v>
-      </c>
       <c r="K101" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L101" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B102" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="D102" t="s">
         <v>111</v>
@@ -6582,13 +6918,16 @@
         <v>10005</v>
       </c>
       <c r="I102" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="K102" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L102" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>112</v>
       </c>
@@ -6611,15 +6950,18 @@
         <v>115</v>
       </c>
       <c r="K103" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L103" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B104" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D104" t="s">
         <v>11</v>
@@ -6628,18 +6970,21 @@
         <v>11378</v>
       </c>
       <c r="I104" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="K104" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L104" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>747</v>
       </c>
       <c r="B105" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="D105" t="s">
         <v>11</v>
@@ -6654,15 +6999,18 @@
         <v>749</v>
       </c>
       <c r="K105" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L105" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
+        <v>952</v>
+      </c>
+      <c r="B106" t="s">
         <v>953</v>
-      </c>
-      <c r="B106" t="s">
-        <v>954</v>
       </c>
       <c r="D106" t="s">
         <v>11</v>
@@ -6671,21 +7019,24 @@
         <v>11421</v>
       </c>
       <c r="I106" t="s">
+        <v>954</v>
+      </c>
+      <c r="J106" t="s">
         <v>955</v>
       </c>
-      <c r="J106" t="s">
-        <v>956</v>
-      </c>
       <c r="K106" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L106" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>767</v>
       </c>
       <c r="B107" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="D107" t="s">
         <v>11</v>
@@ -6700,15 +7051,18 @@
         <v>769</v>
       </c>
       <c r="K107" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L107" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
+        <v>827</v>
+      </c>
+      <c r="B108" t="s">
         <v>828</v>
-      </c>
-      <c r="B108" t="s">
-        <v>829</v>
       </c>
       <c r="D108" t="s">
         <v>16</v>
@@ -6717,21 +7071,24 @@
         <v>10301</v>
       </c>
       <c r="I108" t="s">
+        <v>829</v>
+      </c>
+      <c r="J108" t="s">
         <v>830</v>
       </c>
-      <c r="J108" t="s">
-        <v>831</v>
-      </c>
       <c r="K108" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L108" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B109" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="D109" t="s">
         <v>16</v>
@@ -6740,21 +7097,24 @@
         <v>10301</v>
       </c>
       <c r="I109" t="s">
+        <v>959</v>
+      </c>
+      <c r="J109" t="s">
         <v>960</v>
       </c>
-      <c r="J109" t="s">
-        <v>961</v>
-      </c>
       <c r="K109" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L109" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B110" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="D110" t="s">
         <v>16</v>
@@ -6763,21 +7123,24 @@
         <v>10301</v>
       </c>
       <c r="I110" t="s">
+        <v>968</v>
+      </c>
+      <c r="J110" t="s">
         <v>969</v>
       </c>
-      <c r="J110" t="s">
-        <v>970</v>
-      </c>
       <c r="K110" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L110" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>760</v>
       </c>
       <c r="B111" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="D111" t="s">
         <v>16</v>
@@ -6789,15 +7152,18 @@
         <v>761</v>
       </c>
       <c r="K111" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L111" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B112" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="D112" t="s">
         <v>16</v>
@@ -6806,18 +7172,21 @@
         <v>10306</v>
       </c>
       <c r="I112" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="K112" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L112" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B113" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="D113" t="s">
         <v>16</v>
@@ -6826,13 +7195,16 @@
         <v>10314</v>
       </c>
       <c r="I113" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="K113" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1001</v>
+      </c>
+      <c r="L113" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>541</v>
       </c>
@@ -6858,10 +7230,13 @@
         <v>174</v>
       </c>
       <c r="K114" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L114" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>201</v>
       </c>
@@ -6884,10 +7259,13 @@
         <v>204</v>
       </c>
       <c r="K115" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L115" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>68</v>
       </c>
@@ -6910,10 +7288,13 @@
         <v>72</v>
       </c>
       <c r="K116" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L116" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>676</v>
       </c>
@@ -6939,10 +7320,13 @@
         <v>680</v>
       </c>
       <c r="K117" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L117" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>598</v>
       </c>
@@ -6968,10 +7352,13 @@
         <v>174</v>
       </c>
       <c r="K118" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L118" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>264</v>
       </c>
@@ -6994,10 +7381,13 @@
         <v>267</v>
       </c>
       <c r="K119" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L119" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>276</v>
       </c>
@@ -7023,15 +7413,18 @@
         <v>245</v>
       </c>
       <c r="K120" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L120" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>655</v>
       </c>
       <c r="B121" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C121" t="s">
         <v>656</v>
@@ -7046,13 +7439,16 @@
         <v>2004</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="K121" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L121" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>279</v>
       </c>
@@ -7075,10 +7471,13 @@
         <v>146</v>
       </c>
       <c r="K122" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L122" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>143</v>
       </c>
@@ -7101,10 +7500,13 @@
         <v>146</v>
       </c>
       <c r="K123" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L123" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>324</v>
       </c>
@@ -7127,10 +7529,13 @@
         <v>146</v>
       </c>
       <c r="K124" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L124" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>64</v>
       </c>
@@ -7153,10 +7558,13 @@
         <v>67</v>
       </c>
       <c r="K125" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L125" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>182</v>
       </c>
@@ -7179,10 +7587,13 @@
         <v>185</v>
       </c>
       <c r="K126" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L126" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>439</v>
       </c>
@@ -7205,10 +7616,13 @@
         <v>442</v>
       </c>
       <c r="K127" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L127" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>179</v>
       </c>
@@ -7231,10 +7645,13 @@
         <v>178</v>
       </c>
       <c r="K128" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L128" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>175</v>
       </c>
@@ -7257,10 +7674,13 @@
         <v>178</v>
       </c>
       <c r="K129" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L129" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>39</v>
       </c>
@@ -7283,10 +7703,13 @@
         <v>42</v>
       </c>
       <c r="K130" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L130" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>635</v>
       </c>
@@ -7312,10 +7735,13 @@
         <v>639</v>
       </c>
       <c r="K131" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L131" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>120</v>
       </c>
@@ -7338,10 +7764,13 @@
         <v>123</v>
       </c>
       <c r="K132" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L132" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>61</v>
       </c>
@@ -7364,10 +7793,13 @@
         <v>60</v>
       </c>
       <c r="K133" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L133" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>193</v>
       </c>
@@ -7390,10 +7822,13 @@
         <v>196</v>
       </c>
       <c r="K134" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L134" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>473</v>
       </c>
@@ -7419,10 +7854,13 @@
         <v>468</v>
       </c>
       <c r="K135" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L135" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>464</v>
       </c>
@@ -7448,10 +7886,13 @@
         <v>468</v>
       </c>
       <c r="K136" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L136" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>621</v>
       </c>
@@ -7477,10 +7918,13 @@
         <v>625</v>
       </c>
       <c r="K137" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L137" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>550</v>
       </c>
@@ -7506,15 +7950,18 @@
         <v>554</v>
       </c>
       <c r="K138" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L138" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B139" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="D139" t="s">
         <v>37</v>
@@ -7523,18 +7970,21 @@
         <v>11201</v>
       </c>
       <c r="I139" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K139" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L139" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>817</v>
       </c>
       <c r="B140" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D140" t="s">
         <v>37</v>
@@ -7546,15 +7996,18 @@
         <v>818</v>
       </c>
       <c r="K140" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L140" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>801</v>
       </c>
       <c r="B141" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D141" t="s">
         <v>37</v>
@@ -7566,15 +8019,18 @@
         <v>802</v>
       </c>
       <c r="K141" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L141" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>653</v>
       </c>
       <c r="B142" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="C142" t="s">
         <v>654</v>
@@ -7592,10 +8048,13 @@
         <v>234</v>
       </c>
       <c r="K142" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L142" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>208</v>
       </c>
@@ -7618,10 +8077,13 @@
         <v>211</v>
       </c>
       <c r="K143" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L143" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>238</v>
       </c>
@@ -7644,10 +8106,13 @@
         <v>234</v>
       </c>
       <c r="K144" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L144" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>386</v>
       </c>
@@ -7670,10 +8135,13 @@
         <v>389</v>
       </c>
       <c r="K145" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L145" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>509</v>
       </c>
@@ -7699,10 +8167,13 @@
         <v>513</v>
       </c>
       <c r="K146" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L146" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>522</v>
       </c>
@@ -7722,13 +8193,16 @@
         <v>2002</v>
       </c>
       <c r="H147" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="K147" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L147" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>108</v>
       </c>
@@ -7748,13 +8222,16 @@
         <v>2018</v>
       </c>
       <c r="H148" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="K148" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L148" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>394</v>
       </c>
@@ -7777,10 +8254,13 @@
         <v>393</v>
       </c>
       <c r="K149" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L149" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>514</v>
       </c>
@@ -7806,15 +8286,18 @@
         <v>518</v>
       </c>
       <c r="K150" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L150" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>810</v>
       </c>
       <c r="B151" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="D151" t="s">
         <v>111</v>
@@ -7829,15 +8312,18 @@
         <v>812</v>
       </c>
       <c r="K151" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L151" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>803</v>
       </c>
       <c r="B152" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="D152" t="s">
         <v>111</v>
@@ -7849,10 +8335,13 @@
         <v>804</v>
       </c>
       <c r="K152" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L152" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>786</v>
       </c>
@@ -7872,15 +8361,18 @@
         <v>789</v>
       </c>
       <c r="K153" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L153" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>730</v>
       </c>
       <c r="B154" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C154" t="s">
         <v>731</v>
@@ -7898,21 +8390,24 @@
         <v>732</v>
       </c>
       <c r="H154" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="K154" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L154" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B155" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C155" t="s">
         <v>1030</v>
-      </c>
-      <c r="B155" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C155" t="s">
-        <v>1031</v>
       </c>
       <c r="D155" t="s">
         <v>11</v>
@@ -7924,21 +8419,24 @@
         <v>2004</v>
       </c>
       <c r="H155" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="K155" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L155" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C156" t="s">
         <v>1021</v>
-      </c>
-      <c r="B156" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C156" t="s">
-        <v>1022</v>
       </c>
       <c r="D156" t="s">
         <v>11</v>
@@ -7950,21 +8448,24 @@
         <v>2004</v>
       </c>
       <c r="G156" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H156" t="s">
         <v>260</v>
       </c>
       <c r="K156" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L156" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>715</v>
       </c>
       <c r="B157" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C157" t="s">
         <v>716</v>
@@ -7985,15 +8486,18 @@
         <v>260</v>
       </c>
       <c r="K157" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L157" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>712</v>
       </c>
       <c r="B158" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C158" t="s">
         <v>713</v>
@@ -8011,13 +8515,16 @@
         <v>714</v>
       </c>
       <c r="H158" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="K158" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L158" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>631</v>
       </c>
@@ -8043,10 +8550,13 @@
         <v>260</v>
       </c>
       <c r="K159" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L159" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>500</v>
       </c>
@@ -8072,10 +8582,13 @@
         <v>149</v>
       </c>
       <c r="K160" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L160" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>456</v>
       </c>
@@ -8101,10 +8614,13 @@
         <v>149</v>
       </c>
       <c r="K161" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L161" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>369</v>
       </c>
@@ -8127,10 +8643,13 @@
         <v>372</v>
       </c>
       <c r="K162" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L162" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>421</v>
       </c>
@@ -8153,10 +8672,13 @@
         <v>420</v>
       </c>
       <c r="K163" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L163" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>417</v>
       </c>
@@ -8179,10 +8701,13 @@
         <v>420</v>
       </c>
       <c r="K164" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L164" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>590</v>
       </c>
@@ -8208,10 +8733,13 @@
         <v>594</v>
       </c>
       <c r="K165" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L165" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>291</v>
       </c>
@@ -8234,10 +8762,13 @@
         <v>33</v>
       </c>
       <c r="K166" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L166" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>285</v>
       </c>
@@ -8260,10 +8791,13 @@
         <v>33</v>
       </c>
       <c r="K167" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L167" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>536</v>
       </c>
@@ -8289,10 +8823,13 @@
         <v>540</v>
       </c>
       <c r="K168" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L168" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>681</v>
       </c>
@@ -8318,10 +8855,13 @@
         <v>685</v>
       </c>
       <c r="K169" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L169" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>137</v>
       </c>
@@ -8344,10 +8884,13 @@
         <v>163</v>
       </c>
       <c r="K170" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L170" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>293</v>
       </c>
@@ -8370,15 +8913,18 @@
         <v>296</v>
       </c>
       <c r="K171" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L171" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>647</v>
       </c>
       <c r="B172" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C172" t="s">
         <v>648</v>
@@ -8393,13 +8939,16 @@
         <v>2001</v>
       </c>
       <c r="H172" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="K172" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L172" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>529</v>
       </c>
@@ -8422,13 +8971,16 @@
         <v>532</v>
       </c>
       <c r="H173" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="K173" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L173" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>525</v>
       </c>
@@ -8451,13 +9003,16 @@
         <v>528</v>
       </c>
       <c r="H174" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="K174" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L174" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>317</v>
       </c>
@@ -8480,10 +9035,13 @@
         <v>87</v>
       </c>
       <c r="K175" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L175" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>504</v>
       </c>
@@ -8509,10 +9067,13 @@
         <v>508</v>
       </c>
       <c r="K176" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L176" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>373</v>
       </c>
@@ -8535,15 +9096,18 @@
         <v>200</v>
       </c>
       <c r="K177" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L177" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>815</v>
       </c>
       <c r="B178" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="D178" t="s">
         <v>11</v>
@@ -8555,15 +9119,18 @@
         <v>816</v>
       </c>
       <c r="K178" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L178" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B179" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D179" t="s">
         <v>11</v>
@@ -8572,21 +9139,24 @@
         <v>11370</v>
       </c>
       <c r="I179" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="K179" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L179" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>770</v>
       </c>
       <c r="B180" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C180" t="s">
         <v>1049</v>
-      </c>
-      <c r="C180" t="s">
-        <v>1050</v>
       </c>
       <c r="D180" t="s">
         <v>16</v>
@@ -8604,15 +9174,18 @@
         <v>771</v>
       </c>
       <c r="K180" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L180" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>649</v>
       </c>
       <c r="B181" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C181" t="s">
         <v>650</v>
@@ -8630,15 +9203,18 @@
         <v>170</v>
       </c>
       <c r="K181" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="182" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L181" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>721</v>
       </c>
       <c r="B182" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C182" t="s">
         <v>722</v>
@@ -8659,10 +9235,13 @@
         <v>170</v>
       </c>
       <c r="K182" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L182" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>95</v>
       </c>
@@ -8685,10 +9264,13 @@
         <v>17</v>
       </c>
       <c r="K183" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L183" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>128</v>
       </c>
@@ -8711,10 +9293,13 @@
         <v>17</v>
       </c>
       <c r="K184" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L184" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>134</v>
       </c>
@@ -8737,10 +9322,13 @@
         <v>17</v>
       </c>
       <c r="K185" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L185" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>43</v>
       </c>
@@ -8763,10 +9351,13 @@
         <v>17</v>
       </c>
       <c r="K186" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L186" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -8789,10 +9380,13 @@
         <v>17</v>
       </c>
       <c r="K187" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L187" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>98</v>
       </c>
@@ -8815,10 +9409,13 @@
         <v>24</v>
       </c>
       <c r="K188" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L188" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>150</v>
       </c>
@@ -8841,10 +9438,13 @@
         <v>24</v>
       </c>
       <c r="K189" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L189" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>28</v>
       </c>
@@ -8867,10 +9467,13 @@
         <v>31</v>
       </c>
       <c r="K190" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L190" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>186</v>
       </c>
@@ -8893,10 +9496,13 @@
         <v>189</v>
       </c>
       <c r="K191" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L191" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>216</v>
       </c>
@@ -8919,10 +9525,13 @@
         <v>219</v>
       </c>
       <c r="K192" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L192" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>339</v>
       </c>
@@ -8945,10 +9554,13 @@
         <v>119</v>
       </c>
       <c r="K193" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L193" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>424</v>
       </c>
@@ -8971,10 +9583,13 @@
         <v>119</v>
       </c>
       <c r="K194" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L194" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>77</v>
       </c>
@@ -8997,10 +9612,13 @@
         <v>76</v>
       </c>
       <c r="K195" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L195" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>224</v>
       </c>
@@ -9023,10 +9641,13 @@
         <v>223</v>
       </c>
       <c r="K196" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L196" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>331</v>
       </c>
@@ -9052,10 +9673,13 @@
         <v>335</v>
       </c>
       <c r="K197" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L197" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>469</v>
       </c>
@@ -9081,10 +9705,13 @@
         <v>170</v>
       </c>
       <c r="K198" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L198" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>167</v>
       </c>
@@ -9107,10 +9734,13 @@
         <v>170</v>
       </c>
       <c r="K199" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L199" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>662</v>
       </c>
@@ -9133,10 +9763,13 @@
         <v>170</v>
       </c>
       <c r="K200" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L200" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>411</v>
       </c>
@@ -9159,10 +9792,13 @@
         <v>83</v>
       </c>
       <c r="K201" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L201" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>359</v>
       </c>
@@ -9185,10 +9821,13 @@
         <v>83</v>
       </c>
       <c r="K202" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L202" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>427</v>
       </c>
@@ -9211,15 +9850,18 @@
         <v>430</v>
       </c>
       <c r="K203" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L203" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B204" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="D204" t="s">
         <v>16</v>
@@ -9228,18 +9870,21 @@
         <v>10301</v>
       </c>
       <c r="I204" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="K204" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L204" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>813</v>
       </c>
       <c r="B205" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="D205" t="s">
         <v>16</v>
@@ -9251,15 +9896,18 @@
         <v>814</v>
       </c>
       <c r="K205" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L205" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B206" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="D206" t="s">
         <v>16</v>
@@ -9268,18 +9916,21 @@
         <v>10306</v>
       </c>
       <c r="I206" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="K206" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L206" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B207" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="D207" t="s">
         <v>16</v>
@@ -9288,18 +9939,21 @@
         <v>10310</v>
       </c>
       <c r="I207" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="K207" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L207" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B208" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D208" t="s">
         <v>16</v>
@@ -9308,13 +9962,16 @@
         <v>10312</v>
       </c>
       <c r="I208" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="K208" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1182</v>
+      </c>
+      <c r="L208" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>376</v>
       </c>
@@ -9337,10 +9994,13 @@
         <v>72</v>
       </c>
       <c r="K209" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="L209" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>460</v>
       </c>
@@ -9366,10 +10026,13 @@
         <v>60</v>
       </c>
       <c r="K210" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="L210" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>34</v>
       </c>
@@ -9392,15 +10055,18 @@
         <v>38</v>
       </c>
       <c r="K211" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="L211" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>776</v>
       </c>
       <c r="B212" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="D212" t="s">
         <v>37</v>
@@ -9415,10 +10081,13 @@
         <v>778</v>
       </c>
       <c r="K212" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="L212" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>251</v>
       </c>
@@ -9444,10 +10113,13 @@
         <v>250</v>
       </c>
       <c r="K213" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="L213" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>497</v>
       </c>
@@ -9473,10 +10145,13 @@
         <v>250</v>
       </c>
       <c r="K214" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="L214" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>246</v>
       </c>
@@ -9502,10 +10177,13 @@
         <v>250</v>
       </c>
       <c r="K215" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="L215" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>254</v>
       </c>
@@ -9531,10 +10209,13 @@
         <v>250</v>
       </c>
       <c r="K216" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="L216" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>327</v>
       </c>
@@ -9557,15 +10238,18 @@
         <v>330</v>
       </c>
       <c r="K217" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="L217" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>706</v>
       </c>
       <c r="B218" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C218" t="s">
         <v>707</v>
@@ -9586,10 +10270,13 @@
         <v>685</v>
       </c>
       <c r="K218" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="L218" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>397</v>
       </c>
@@ -9612,10 +10299,13 @@
         <v>372</v>
       </c>
       <c r="K219" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="L219" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>197</v>
       </c>
@@ -9638,15 +10328,18 @@
         <v>200</v>
       </c>
       <c r="K220" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="L220" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B221" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D221" t="s">
         <v>11</v>
@@ -9655,18 +10348,21 @@
         <v>11355</v>
       </c>
       <c r="I221" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="K221" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="L221" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B222" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D222" t="s">
         <v>11</v>
@@ -9675,18 +10371,21 @@
         <v>11360</v>
       </c>
       <c r="I222" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="K222" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="L222" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B223" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="D223" t="s">
         <v>11</v>
@@ -9695,13 +10394,16 @@
         <v>11414</v>
       </c>
       <c r="I223" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="K223" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="L223" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>131</v>
       </c>
@@ -9724,10 +10426,13 @@
         <v>17</v>
       </c>
       <c r="K224" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="L224" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>644</v>
       </c>
@@ -9750,10 +10455,13 @@
         <v>24</v>
       </c>
       <c r="K225" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="L225" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>190</v>
       </c>
@@ -9776,15 +10484,18 @@
         <v>170</v>
       </c>
       <c r="K226" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="L226" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B227" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="D227" t="s">
         <v>71</v>
@@ -9793,18 +10504,21 @@
         <v>10454</v>
       </c>
       <c r="I227" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="K227" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L227" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>799</v>
       </c>
       <c r="B228" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="D228" t="s">
         <v>71</v>
@@ -9816,15 +10530,18 @@
         <v>800</v>
       </c>
       <c r="K228" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L228" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
+        <v>874</v>
+      </c>
+      <c r="B229" t="s">
         <v>875</v>
-      </c>
-      <c r="B229" t="s">
-        <v>876</v>
       </c>
       <c r="D229" t="s">
         <v>71</v>
@@ -9833,16 +10550,19 @@
         <v>10473</v>
       </c>
       <c r="I229" t="s">
+        <v>876</v>
+      </c>
+      <c r="J229" t="s">
         <v>877</v>
       </c>
-      <c r="J229" t="s">
-        <v>878</v>
-      </c>
       <c r="K229" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L229" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>355</v>
       </c>
@@ -9865,10 +10585,13 @@
         <v>358</v>
       </c>
       <c r="K230" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L230" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>772</v>
       </c>
@@ -9888,15 +10611,18 @@
         <v>775</v>
       </c>
       <c r="K231" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L231" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>823</v>
+        <v>1207</v>
       </c>
       <c r="B232" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D232" t="s">
         <v>37</v>
@@ -9905,18 +10631,21 @@
         <v>11201</v>
       </c>
       <c r="I232" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="K232" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L232" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
+        <v>914</v>
+      </c>
+      <c r="B233" t="s">
         <v>915</v>
-      </c>
-      <c r="B233" t="s">
-        <v>916</v>
       </c>
       <c r="D233" t="s">
         <v>37</v>
@@ -9925,18 +10654,21 @@
         <v>11207</v>
       </c>
       <c r="I233" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="K233" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L233" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B234" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="D234" t="s">
         <v>37</v>
@@ -9948,15 +10680,18 @@
         <v>790</v>
       </c>
       <c r="K234" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L234" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B235" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="D235" t="s">
         <v>37</v>
@@ -9965,21 +10700,24 @@
         <v>11220</v>
       </c>
       <c r="I235" t="s">
+        <v>839</v>
+      </c>
+      <c r="J235" t="s">
         <v>840</v>
       </c>
-      <c r="J235" t="s">
-        <v>841</v>
-      </c>
       <c r="K235" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L235" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
+        <v>867</v>
+      </c>
+      <c r="B236" t="s">
         <v>868</v>
-      </c>
-      <c r="B236" t="s">
-        <v>869</v>
       </c>
       <c r="D236" t="s">
         <v>37</v>
@@ -9988,18 +10726,21 @@
         <v>11225</v>
       </c>
       <c r="I236" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="K236" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L236" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B237" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="D237" t="s">
         <v>111</v>
@@ -10008,21 +10749,24 @@
         <v>10006</v>
       </c>
       <c r="I237" t="s">
+        <v>897</v>
+      </c>
+      <c r="J237" t="s">
         <v>898</v>
       </c>
-      <c r="J237" t="s">
-        <v>899</v>
-      </c>
       <c r="K237" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L237" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>752</v>
       </c>
       <c r="B238" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="D238" t="s">
         <v>111</v>
@@ -10037,15 +10781,18 @@
         <v>754</v>
       </c>
       <c r="K238" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L238" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
+        <v>870</v>
+      </c>
+      <c r="B239" t="s">
         <v>871</v>
-      </c>
-      <c r="B239" t="s">
-        <v>872</v>
       </c>
       <c r="D239" t="s">
         <v>111</v>
@@ -10054,21 +10801,24 @@
         <v>10013</v>
       </c>
       <c r="I239" t="s">
+        <v>872</v>
+      </c>
+      <c r="J239" t="s">
         <v>873</v>
       </c>
-      <c r="J239" t="s">
-        <v>874</v>
-      </c>
       <c r="K239" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L239" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>782</v>
       </c>
       <c r="B240" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="D240" t="s">
         <v>111</v>
@@ -10080,15 +10830,18 @@
         <v>783</v>
       </c>
       <c r="K240" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L240" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
+        <v>989</v>
+      </c>
+      <c r="B241" t="s">
         <v>990</v>
-      </c>
-      <c r="B241" t="s">
-        <v>991</v>
       </c>
       <c r="D241" t="s">
         <v>111</v>
@@ -10097,21 +10850,24 @@
         <v>10025</v>
       </c>
       <c r="I241" t="s">
+        <v>991</v>
+      </c>
+      <c r="J241" t="s">
         <v>992</v>
       </c>
-      <c r="J241" t="s">
-        <v>993</v>
-      </c>
       <c r="K241" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L241" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="242" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B242" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D242" t="s">
         <v>111</v>
@@ -10120,21 +10876,24 @@
         <v>10033</v>
       </c>
       <c r="I242" t="s">
+        <v>852</v>
+      </c>
+      <c r="J242" t="s">
         <v>853</v>
       </c>
-      <c r="J242" t="s">
-        <v>854</v>
-      </c>
       <c r="K242" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L242" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="243" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B243" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="D243" t="s">
         <v>111</v>
@@ -10143,18 +10902,21 @@
         <v>10044</v>
       </c>
       <c r="I243" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="K243" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L243" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="244" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
+        <v>970</v>
+      </c>
+      <c r="B244" t="s">
         <v>971</v>
-      </c>
-      <c r="B244" t="s">
-        <v>972</v>
       </c>
       <c r="D244" t="s">
         <v>111</v>
@@ -10163,21 +10925,24 @@
         <v>10048</v>
       </c>
       <c r="I244" t="s">
+        <v>972</v>
+      </c>
+      <c r="J244" t="s">
         <v>973</v>
       </c>
-      <c r="J244" t="s">
-        <v>974</v>
-      </c>
       <c r="K244" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L244" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="245" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>745</v>
       </c>
       <c r="B245" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D245" t="s">
         <v>111</v>
@@ -10189,12 +10954,15 @@
         <v>746</v>
       </c>
       <c r="K245" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L245" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="246" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B246" t="s">
         <v>533</v>
@@ -10218,12 +10986,15 @@
         <v>557</v>
       </c>
       <c r="K246" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L246" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="247" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B247" t="s">
         <v>533</v>
@@ -10247,15 +11018,18 @@
         <v>33</v>
       </c>
       <c r="K247" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L247" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="248" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B248" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D248" t="s">
         <v>11</v>
@@ -10264,21 +11038,24 @@
         <v>11377</v>
       </c>
       <c r="I248" t="s">
+        <v>886</v>
+      </c>
+      <c r="J248" t="s">
         <v>887</v>
       </c>
-      <c r="J248" t="s">
-        <v>888</v>
-      </c>
       <c r="K248" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L248" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="249" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B249" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D249" t="s">
         <v>11</v>
@@ -10287,18 +11064,21 @@
         <v>11694</v>
       </c>
       <c r="I249" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="K249" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L249" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="250" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B250" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="D250" t="s">
         <v>11</v>
@@ -10307,21 +11087,24 @@
         <v>11694</v>
       </c>
       <c r="I250" t="s">
+        <v>926</v>
+      </c>
+      <c r="J250" t="s">
         <v>927</v>
       </c>
-      <c r="J250" t="s">
-        <v>928</v>
-      </c>
       <c r="K250" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L250" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="251" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B251" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="D251" t="s">
         <v>16</v>
@@ -10330,18 +11113,21 @@
         <v>10304</v>
       </c>
       <c r="I251" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="K251" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L251" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="252" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
+        <v>841</v>
+      </c>
+      <c r="B252" t="s">
         <v>842</v>
-      </c>
-      <c r="B252" t="s">
-        <v>843</v>
       </c>
       <c r="D252" t="s">
         <v>16</v>
@@ -10350,21 +11136,24 @@
         <v>10308</v>
       </c>
       <c r="I252" t="s">
+        <v>843</v>
+      </c>
+      <c r="J252" t="s">
         <v>844</v>
       </c>
-      <c r="J252" t="s">
-        <v>845</v>
-      </c>
       <c r="K252" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L252" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="253" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>791</v>
       </c>
       <c r="B253" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="D253" t="s">
         <v>16</v>
@@ -10376,15 +11165,18 @@
         <v>792</v>
       </c>
       <c r="K253" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L253" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="254" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B254" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="D254" t="s">
         <v>16</v>
@@ -10393,16 +11185,19 @@
         <v>10314</v>
       </c>
       <c r="I254" t="s">
+        <v>825</v>
+      </c>
+      <c r="J254" t="s">
         <v>826</v>
       </c>
-      <c r="J254" t="s">
-        <v>827</v>
-      </c>
       <c r="K254" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1180</v>
+      </c>
+      <c r="L254" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="255" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>558</v>
       </c>
@@ -10428,10 +11223,13 @@
         <v>562</v>
       </c>
       <c r="K255" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L255" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="256" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>495</v>
       </c>
@@ -10457,10 +11255,13 @@
         <v>72</v>
       </c>
       <c r="K256" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L256" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>477</v>
       </c>
@@ -10486,10 +11287,13 @@
         <v>72</v>
       </c>
       <c r="K257" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L257" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>171</v>
       </c>
@@ -10512,10 +11316,13 @@
         <v>174</v>
       </c>
       <c r="K258" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L258" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>362</v>
       </c>
@@ -10538,10 +11345,13 @@
         <v>365</v>
       </c>
       <c r="K259" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L259" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>320</v>
       </c>
@@ -10564,10 +11374,13 @@
         <v>323</v>
       </c>
       <c r="K260" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L260" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>563</v>
       </c>
@@ -10593,10 +11406,13 @@
         <v>567</v>
       </c>
       <c r="K261" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L261" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="262" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>241</v>
       </c>
@@ -10622,10 +11438,13 @@
         <v>245</v>
       </c>
       <c r="K262" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L262" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="263" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>268</v>
       </c>
@@ -10648,10 +11467,13 @@
         <v>271</v>
       </c>
       <c r="K263" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L263" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="264" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>88</v>
       </c>
@@ -10674,10 +11496,13 @@
         <v>91</v>
       </c>
       <c r="K264" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L264" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="265" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>435</v>
       </c>
@@ -10700,10 +11525,13 @@
         <v>438</v>
       </c>
       <c r="K265" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L265" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="266" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>431</v>
       </c>
@@ -10726,10 +11554,13 @@
         <v>434</v>
       </c>
       <c r="K266" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L266" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="267" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>101</v>
       </c>
@@ -10752,10 +11583,13 @@
         <v>104</v>
       </c>
       <c r="K267" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L267" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="268" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>481</v>
       </c>
@@ -10781,10 +11615,13 @@
         <v>485</v>
       </c>
       <c r="K268" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L268" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="269" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>57</v>
       </c>
@@ -10807,10 +11644,13 @@
         <v>60</v>
       </c>
       <c r="K269" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L269" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="270" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>640</v>
       </c>
@@ -10836,10 +11676,13 @@
         <v>60</v>
       </c>
       <c r="K270" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L270" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="271" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>105</v>
       </c>
@@ -10862,10 +11705,13 @@
         <v>87</v>
       </c>
       <c r="K271" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L271" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="272" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>124</v>
       </c>
@@ -10888,10 +11734,13 @@
         <v>127</v>
       </c>
       <c r="K272" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L272" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="273" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>308</v>
       </c>
@@ -10914,12 +11763,15 @@
         <v>127</v>
       </c>
       <c r="K273" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L273" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B274" t="s">
         <v>164</v>
@@ -10940,12 +11792,15 @@
         <v>166</v>
       </c>
       <c r="K274" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L274" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="275" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B275" t="s">
         <v>595</v>
@@ -10969,10 +11824,13 @@
         <v>166</v>
       </c>
       <c r="K275" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L275" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="276" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>390</v>
       </c>
@@ -10995,15 +11853,18 @@
         <v>393</v>
       </c>
       <c r="K276" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L276" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="277" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B277" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D277" t="s">
         <v>111</v>
@@ -11012,18 +11873,21 @@
         <v>10019</v>
       </c>
       <c r="I277" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="K277" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L277" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="278" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
+        <v>899</v>
+      </c>
+      <c r="B278" t="s">
         <v>900</v>
-      </c>
-      <c r="B278" t="s">
-        <v>901</v>
       </c>
       <c r="D278" t="s">
         <v>111</v>
@@ -11032,13 +11896,16 @@
         <v>10038</v>
       </c>
       <c r="I278" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="K278" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L278" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="279" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>8</v>
       </c>
@@ -11061,10 +11928,13 @@
         <v>12</v>
       </c>
       <c r="K279" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L279" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="280" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>297</v>
       </c>
@@ -11087,10 +11957,13 @@
         <v>300</v>
       </c>
       <c r="K280" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L280" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="281" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>581</v>
       </c>
@@ -11116,10 +11989,13 @@
         <v>585</v>
       </c>
       <c r="K281" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L281" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="282" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>403</v>
       </c>
@@ -11142,10 +12018,13 @@
         <v>406</v>
       </c>
       <c r="K282" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L282" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="283" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>451</v>
       </c>
@@ -11171,10 +12050,13 @@
         <v>455</v>
       </c>
       <c r="K283" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L283" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="284" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>46</v>
       </c>
@@ -11197,10 +12079,13 @@
         <v>33</v>
       </c>
       <c r="K284" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L284" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="285" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>443</v>
       </c>
@@ -11226,10 +12111,13 @@
         <v>33</v>
       </c>
       <c r="K285" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L285" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="286" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>160</v>
       </c>
@@ -11252,10 +12140,13 @@
         <v>163</v>
       </c>
       <c r="K286" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L286" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="287" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>379</v>
       </c>
@@ -11278,10 +12169,13 @@
         <v>163</v>
       </c>
       <c r="K287" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L287" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="288" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>352</v>
       </c>
@@ -11304,10 +12198,13 @@
         <v>163</v>
       </c>
       <c r="K288" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L288" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="289" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>313</v>
       </c>
@@ -11330,10 +12227,13 @@
         <v>316</v>
       </c>
       <c r="K289" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L289" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="290" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>53</v>
       </c>
@@ -11356,10 +12256,13 @@
         <v>56</v>
       </c>
       <c r="K290" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L290" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="291" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>84</v>
       </c>
@@ -11382,10 +12285,13 @@
         <v>87</v>
       </c>
       <c r="K291" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L291" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="292" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>447</v>
       </c>
@@ -11411,10 +12317,13 @@
         <v>87</v>
       </c>
       <c r="K292" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L292" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="293" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>577</v>
       </c>
@@ -11440,10 +12349,13 @@
         <v>345</v>
       </c>
       <c r="K293" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L293" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="294" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>568</v>
       </c>
@@ -11469,10 +12381,13 @@
         <v>345</v>
       </c>
       <c r="K294" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L294" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="295" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>382</v>
       </c>
@@ -11495,10 +12410,13 @@
         <v>385</v>
       </c>
       <c r="K295" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L295" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="296" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>13</v>
       </c>
@@ -11521,10 +12439,13 @@
         <v>17</v>
       </c>
       <c r="K296" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L296" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="297" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>140</v>
       </c>
@@ -11547,10 +12468,13 @@
         <v>17</v>
       </c>
       <c r="K297" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L297" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="298" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>572</v>
       </c>
@@ -11576,10 +12500,13 @@
         <v>576</v>
       </c>
       <c r="K298" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L298" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="299" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>25</v>
       </c>
@@ -11602,10 +12529,13 @@
         <v>24</v>
       </c>
       <c r="K299" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L299" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="300" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>21</v>
       </c>
@@ -11628,10 +12558,13 @@
         <v>24</v>
       </c>
       <c r="K300" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L300" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="301" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>407</v>
       </c>
@@ -11654,10 +12587,13 @@
         <v>410</v>
       </c>
       <c r="K301" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L301" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="302" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>668</v>
       </c>
@@ -11680,10 +12616,13 @@
         <v>189</v>
       </c>
       <c r="K302" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L302" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="303" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>272</v>
       </c>
@@ -11706,10 +12645,13 @@
         <v>275</v>
       </c>
       <c r="K303" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L303" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="304" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>400</v>
       </c>
@@ -11732,10 +12674,13 @@
         <v>119</v>
       </c>
       <c r="K304" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L304" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="305" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>116</v>
       </c>
@@ -11758,10 +12703,13 @@
         <v>119</v>
       </c>
       <c r="K305" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L305" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="306" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>92</v>
       </c>
@@ -11784,10 +12732,13 @@
         <v>76</v>
       </c>
       <c r="K306" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L306" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="307" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>665</v>
       </c>
@@ -11810,10 +12761,13 @@
         <v>630</v>
       </c>
       <c r="K307" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L307" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="308" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>626</v>
       </c>
@@ -11839,10 +12793,13 @@
         <v>630</v>
       </c>
       <c r="K308" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L308" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="309" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>336</v>
       </c>
@@ -11865,10 +12822,13 @@
         <v>335</v>
       </c>
       <c r="K309" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L309" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="310" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>617</v>
       </c>
@@ -11894,10 +12854,13 @@
         <v>170</v>
       </c>
       <c r="K310" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L310" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="311" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>80</v>
       </c>
@@ -11920,10 +12883,13 @@
         <v>83</v>
       </c>
       <c r="K311" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
+        <v>998</v>
+      </c>
+      <c r="L311" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="312" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>282</v>
       </c>
@@ -11946,10 +12912,13 @@
         <v>146</v>
       </c>
       <c r="K312" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
+        <v>999</v>
+      </c>
+      <c r="L312" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="313" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>486</v>
       </c>
@@ -11975,10 +12944,13 @@
         <v>185</v>
       </c>
       <c r="K313" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
+        <v>999</v>
+      </c>
+      <c r="L313" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="314" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>304</v>
       </c>
@@ -12001,10 +12973,13 @@
         <v>307</v>
       </c>
       <c r="K314" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
+        <v>999</v>
+      </c>
+      <c r="L314" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="315" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>49</v>
       </c>
@@ -12027,12 +13002,15 @@
         <v>52</v>
       </c>
       <c r="K315" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
+        <v>999</v>
+      </c>
+      <c r="L315" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="316" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B316" t="s">
         <v>311</v>
@@ -12053,12 +13031,15 @@
         <v>149</v>
       </c>
       <c r="K316" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
+        <v>999</v>
+      </c>
+      <c r="L316" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="317" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B317" t="s">
         <v>147</v>
@@ -12079,10 +13060,13 @@
         <v>149</v>
       </c>
       <c r="K317" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
+        <v>999</v>
+      </c>
+      <c r="L317" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="318" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>349</v>
       </c>
@@ -12105,10 +13089,13 @@
         <v>33</v>
       </c>
       <c r="K318" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
+        <v>999</v>
+      </c>
+      <c r="L318" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="319" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>288</v>
       </c>
@@ -12131,10 +13118,13 @@
         <v>33</v>
       </c>
       <c r="K319" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
+        <v>999</v>
+      </c>
+      <c r="L319" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="320" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>686</v>
       </c>
@@ -12160,10 +13150,13 @@
         <v>690</v>
       </c>
       <c r="K320" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.2">
+        <v>999</v>
+      </c>
+      <c r="L320" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="321" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>366</v>
       </c>
@@ -12186,10 +13179,13 @@
         <v>17</v>
       </c>
       <c r="K321" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.2">
+        <v>999</v>
+      </c>
+      <c r="L321" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="322" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>157</v>
       </c>
@@ -12212,10 +13208,13 @@
         <v>31</v>
       </c>
       <c r="K322" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.2">
+        <v>999</v>
+      </c>
+      <c r="L322" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="323" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>301</v>
       </c>
@@ -12238,10 +13237,13 @@
         <v>275</v>
       </c>
       <c r="K323" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.2">
+        <v>999</v>
+      </c>
+      <c r="L323" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="324" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>220</v>
       </c>
@@ -12264,10 +13266,13 @@
         <v>223</v>
       </c>
       <c r="K324" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.2">
+        <v>999</v>
+      </c>
+      <c r="L324" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="325" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>659</v>
       </c>
@@ -12290,7 +13295,10 @@
         <v>170</v>
       </c>
       <c r="K325" t="s">
-        <v>1000</v>
+        <v>999</v>
+      </c>
+      <c r="L325" t="s">
+        <v>1198</v>
       </c>
     </row>
   </sheetData>
@@ -12298,5 +13306,6 @@
     <sortCondition ref="K1:K325"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/data/total_edits.xlsx
+++ b/data/total_edits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/LLopez-Jensen/Documents/GitHub/9-11-memorials/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB570EB-524E-C940-85AD-3F7250DCFBBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59AEA47E-0E39-C34D-9F9B-6449225BD071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40800" yWindow="1360" windowWidth="38400" windowHeight="19180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2286" uniqueCount="1208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2502" uniqueCount="1307">
   <si>
     <t>new_name</t>
   </si>
@@ -3788,12 +3788,309 @@
   <si>
     <t>memorial_form</t>
   </si>
+  <si>
+    <t>Firemen's Memorial 9/11 Remembrance Way</t>
+  </si>
+  <si>
+    <t>At the intersection of Riverside Drive and West 100th Street</t>
+  </si>
+  <si>
+    <t>Abreu</t>
+  </si>
+  <si>
+    <t>geometry</t>
+  </si>
+  <si>
+    <t>Never Forget Way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At the intersection of 84th Street and 157th Street </t>
+  </si>
+  <si>
+    <t>Tribute Park Way</t>
+  </si>
+  <si>
+    <t>At the intersection of Beach Channel Drive and Beach 116th Street</t>
+  </si>
+  <si>
+    <t>Tunnel to Towers 5K Run &amp; Walk 9/11 Memorial Way </t>
+  </si>
+  <si>
+    <t>At the intersection of Hamilton Avenue and Bowne Street</t>
+  </si>
+  <si>
+    <t>Avilés</t>
+  </si>
+  <si>
+    <t>St. Michael's Cemetery Queens Firefighter Memorial Way</t>
+  </si>
+  <si>
+    <t>At the entrance of St. Michael’s Cemetery and Astoria Boulevard South</t>
+  </si>
+  <si>
+    <t>Angels Circle</t>
+  </si>
+  <si>
+    <t>At the intersection of Hylan Boulevard and Fingerboard Road</t>
+  </si>
+  <si>
+    <t>Monsignor Farrell H.S. 9/11 Wall of Remembrance Way</t>
+  </si>
+  <si>
+    <t>At the intersection of Amber Street and Amboy Road</t>
+  </si>
+  <si>
+    <t>Poly Prep Memorial 9/11 Garden of Remembrance Way</t>
+  </si>
+  <si>
+    <t>At the intersection of 7th Avenue and 92nd Street</t>
+  </si>
+  <si>
+    <t>Endor Community Garden 9/11 Memorial Way</t>
+  </si>
+  <si>
+    <t>At the intersection of Fieldston Road and West 253rd Street</t>
+  </si>
+  <si>
+    <t>Dinowitz</t>
+  </si>
+  <si>
+    <t>Lehman College 9/11 Memorial Way</t>
+  </si>
+  <si>
+    <t>At the intersection of Bedford Park Boulevard West and Goulden Avenue</t>
+  </si>
+  <si>
+    <t>Conselyea 9/11 Memorial Way </t>
+  </si>
+  <si>
+    <t>At the intersection of Conselyea Street and Graham Avenue</t>
+  </si>
+  <si>
+    <t>POINT (-73.94451996838146 40.715270148061194)</t>
+  </si>
+  <si>
+    <t>Staten Island September 11 Postcards Memorial Way</t>
+  </si>
+  <si>
+    <t>At the intersection of Richmond Terrace and Hamilton Avenue</t>
+  </si>
+  <si>
+    <t>POINT (-74.07772478358004 40.64556522080595)</t>
+  </si>
+  <si>
+    <t>Roosevelt Island 9/11 Memorial &amp; Remembrance Tree Way</t>
+  </si>
+  <si>
+    <t>Adjacent to Good Shepherd Plaza</t>
+  </si>
+  <si>
+    <t>Main Street</t>
+  </si>
+  <si>
+    <t>Menin</t>
+  </si>
+  <si>
+    <t>POINT (-73.94989056358142 40.76162612656952)</t>
+  </si>
+  <si>
+    <t>East Side 9/11 Remembrance Way</t>
+  </si>
+  <si>
+    <t>At the intersection of East 86th Street and East End Avenue</t>
+  </si>
+  <si>
+    <t>Fresh Kills 9/11 Recovery Heroes Way </t>
+  </si>
+  <si>
+    <t>At the intersection of West Service Road and Muldoon Avenue</t>
+  </si>
+  <si>
+    <t>Marine Park 9/11 Memorial Way</t>
+  </si>
+  <si>
+    <t>At the intersection of Madison Place and Fillmore Avenue</t>
+  </si>
+  <si>
+    <t>Narcisse</t>
+  </si>
+  <si>
+    <t>POINT (-73.9383143809391 40.60827590368888)</t>
+  </si>
+  <si>
+    <t>Brooklyn 9/11 Wall of Remembrance Way</t>
+  </si>
+  <si>
+    <t>At the intersection of Surf Avenue and West 17th Street</t>
+  </si>
+  <si>
+    <t>Santosuosso</t>
+  </si>
+  <si>
+    <t>September 11 Memorial Square Way</t>
+  </si>
+  <si>
+    <t>At the intersection of West 5th Street and Surf Avenue</t>
+  </si>
+  <si>
+    <t>POINT (-73.97347326568851 40.574793337828254)</t>
+  </si>
+  <si>
+    <t>Bensonhurst Seth Low Park 9/11 Memorial Way</t>
+  </si>
+  <si>
+    <t>At the intersection of Avenue P and West 12th Street</t>
+  </si>
+  <si>
+    <t>Zhuang</t>
+  </si>
+  <si>
+    <t>Marsh and McLennan September 11th Memorial Way</t>
+  </si>
+  <si>
+    <t>At the intersection of West 46th Street and 6th Avenue</t>
+  </si>
+  <si>
+    <t>Maloney</t>
+  </si>
+  <si>
+    <t>POINT (-73.98224631478139 40.757425753706684)</t>
+  </si>
+  <si>
+    <t>Squad 18 September 11th Memorial Way</t>
+  </si>
+  <si>
+    <t>Between 6th Avenue and 5th Avenue</t>
+  </si>
+  <si>
+    <t>Epstein</t>
+  </si>
+  <si>
+    <t>Ladder 3 September 11th Memorial Way</t>
+  </si>
+  <si>
+    <t>Between 3rd Avenue and 4th Avenue</t>
+  </si>
+  <si>
+    <t>Engine 22 / Ladder 13 September 11th Memorial Way</t>
+  </si>
+  <si>
+    <t>Between Lexington Avenue and 3rd Avenue</t>
+  </si>
+  <si>
+    <t>East 85th Street</t>
+  </si>
+  <si>
+    <t>East 13th Street</t>
+  </si>
+  <si>
+    <t>West 10th Street</t>
+  </si>
+  <si>
+    <t>EMS Station 49 September 11th Memorial Way</t>
+  </si>
+  <si>
+    <t>Between 19th Avenue and 20th Avenue</t>
+  </si>
+  <si>
+    <t>Rescue 5 September 11th Memorial Way</t>
+  </si>
+  <si>
+    <t>Between Oder Avenue and Targee Street</t>
+  </si>
+  <si>
+    <t>9/11 Beacon Memorial Way</t>
+  </si>
+  <si>
+    <t>At the intersection of Shore Road and Bay Ridge Avenue</t>
+  </si>
+  <si>
+    <t>POINT (-74.03596427306019 40.63883748889044)</t>
+  </si>
+  <si>
+    <t>start</t>
+  </si>
+  <si>
+    <t>end</t>
+  </si>
+  <si>
+    <t>POINT (-73.97314859750115 40.79858694475294)</t>
+  </si>
+  <si>
+    <t>POINT (-73.84910050281337 40.661481243608826)</t>
+  </si>
+  <si>
+    <t>POINT (-73.83825259504441 40.58181889224658)</t>
+  </si>
+  <si>
+    <t>POINT (-74.00555558287978 40.68100077500471)</t>
+  </si>
+  <si>
+    <t>POINT (-73.89715532361149 40.76660122134801)</t>
+  </si>
+  <si>
+    <t>POINT (-74.07251538932157 40.601655081352355)</t>
+  </si>
+  <si>
+    <t>POINT (-74.12716817398173 40.56778122218683)</t>
+  </si>
+  <si>
+    <t>POINT (-74.02284094514471 40.614775824590346)</t>
+  </si>
+  <si>
+    <t>POINT (-74.19391782651174 40.5667438903575)</t>
+  </si>
+  <si>
+    <t>POINT (-73.90022863164418 40.77560036479045)</t>
+  </si>
+  <si>
+    <t>POINT (-73.9021024793533 40.90076886734074)</t>
+  </si>
+  <si>
+    <t>POINT (-73.89407603824088 40.875603362261145)</t>
+  </si>
+  <si>
+    <t>POINT (-73.98453833262032 40.57538528908763)</t>
+  </si>
+  <si>
+    <t>POINT (-73.9853495818905 40.607523468135895)</t>
+  </si>
+  <si>
+    <t>POINT (-73.9987125514245 40.734813559460264)</t>
+  </si>
+  <si>
+    <t>POINT (-73.98984980092514 40.73353631083037)</t>
+  </si>
+  <si>
+    <t>POINT (-73.95447935004985 40.77815058906401)</t>
+  </si>
+  <si>
+    <t>POINT (-73.95608216529523 40.77883248746682)</t>
+  </si>
+  <si>
+    <t>POINT (-73.89799472965898 40.77727683934558)</t>
+  </si>
+  <si>
+    <t>POINT (-74.08944501459405 40.60771081802627)</t>
+  </si>
+  <si>
+    <t>POINT (-73.98768892555492 40.73262458050335)</t>
+  </si>
+  <si>
+    <t>POINT (-74.08876385281383 40.607303550504824)</t>
+  </si>
+  <si>
+    <t>POINT (-73.9954991928788 40.733461038130734)</t>
+  </si>
+  <si>
+    <t>POINT (-73.94477273249007 40.77495533249186)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3808,6 +4105,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Grande"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3830,7 +4134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3838,6 +4142,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3853,6 +4158,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4142,7 +4451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L325"/>
+  <dimension ref="A1:O351"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.83203125" customWidth="1"/>
@@ -4152,7 +4461,7 @@
     <col min="5" max="10" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4189,8 +4498,17 @@
       <c r="L1" s="1" t="s">
         <v>1207</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M1" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>324</v>
       </c>
@@ -4219,7 +4537,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>331</v>
       </c>
@@ -4251,7 +4569,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>327</v>
       </c>
@@ -4280,7 +4598,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>443</v>
       </c>
@@ -4312,7 +4630,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>447</v>
       </c>
@@ -4344,7 +4662,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>336</v>
       </c>
@@ -4373,7 +4691,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>153</v>
       </c>
@@ -4402,7 +4720,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>143</v>
       </c>
@@ -4431,7 +4749,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>317</v>
       </c>
@@ -4460,7 +4778,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>150</v>
       </c>
@@ -4489,7 +4807,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>320</v>
       </c>
@@ -4518,7 +4836,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>640</v>
       </c>
@@ -4550,7 +4868,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>308</v>
       </c>
@@ -4579,7 +4897,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>313</v>
       </c>
@@ -4608,7 +4926,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>140</v>
       </c>
@@ -13180,7 +13498,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>841</v>
       </c>
@@ -13206,7 +13524,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>791</v>
       </c>
@@ -13229,7 +13547,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>824</v>
       </c>
@@ -13255,7 +13573,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>856</v>
       </c>
@@ -13278,7 +13596,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>899</v>
       </c>
@@ -13299,6 +13617,853 @@
       </c>
       <c r="L325" t="s">
         <v>1203</v>
+      </c>
+    </row>
+    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A326" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C326" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D326" t="s">
+        <v>111</v>
+      </c>
+      <c r="E326">
+        <v>10025</v>
+      </c>
+      <c r="F326">
+        <v>2026</v>
+      </c>
+      <c r="G326" t="s">
+        <v>334</v>
+      </c>
+      <c r="H326" t="s">
+        <v>1210</v>
+      </c>
+      <c r="K326" t="s">
+        <v>1182</v>
+      </c>
+      <c r="L326" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M326" s="3" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A327" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C327" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D327" t="s">
+        <v>11</v>
+      </c>
+      <c r="E327">
+        <v>11414</v>
+      </c>
+      <c r="F327">
+        <v>2026</v>
+      </c>
+      <c r="G327" t="s">
+        <v>334</v>
+      </c>
+      <c r="H327" t="s">
+        <v>12</v>
+      </c>
+      <c r="K327" t="s">
+        <v>1180</v>
+      </c>
+      <c r="L327" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M327" s="3" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A328" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C328" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D328" t="s">
+        <v>11</v>
+      </c>
+      <c r="E328">
+        <v>11694</v>
+      </c>
+      <c r="F328">
+        <v>2026</v>
+      </c>
+      <c r="G328" t="s">
+        <v>334</v>
+      </c>
+      <c r="H328" t="s">
+        <v>12</v>
+      </c>
+      <c r="K328" t="s">
+        <v>1180</v>
+      </c>
+      <c r="L328" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M328" s="3" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="329" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A329" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C329" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D329" t="s">
+        <v>37</v>
+      </c>
+      <c r="E329">
+        <v>11231</v>
+      </c>
+      <c r="F329">
+        <v>2026</v>
+      </c>
+      <c r="G329" t="s">
+        <v>334</v>
+      </c>
+      <c r="H329" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="K329" t="s">
+        <v>1180</v>
+      </c>
+      <c r="L329" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M329" s="3" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A330" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C330" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D330" t="s">
+        <v>11</v>
+      </c>
+      <c r="E330">
+        <v>11103</v>
+      </c>
+      <c r="F330">
+        <v>2026</v>
+      </c>
+      <c r="G330" t="s">
+        <v>334</v>
+      </c>
+      <c r="H330" t="s">
+        <v>149</v>
+      </c>
+      <c r="K330" t="s">
+        <v>1182</v>
+      </c>
+      <c r="L330" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M330" s="3" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A331" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C331" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D331" t="s">
+        <v>16</v>
+      </c>
+      <c r="E331">
+        <v>10305</v>
+      </c>
+      <c r="F331">
+        <v>2026</v>
+      </c>
+      <c r="G331" t="s">
+        <v>334</v>
+      </c>
+      <c r="H331" t="s">
+        <v>24</v>
+      </c>
+      <c r="K331" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L331" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M331" s="3" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A332" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C332" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D332" t="s">
+        <v>16</v>
+      </c>
+      <c r="E332">
+        <v>10306</v>
+      </c>
+      <c r="F332">
+        <v>2026</v>
+      </c>
+      <c r="G332" t="s">
+        <v>334</v>
+      </c>
+      <c r="H332" t="s">
+        <v>24</v>
+      </c>
+      <c r="K332" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L332" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M332" s="3" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A333" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C333" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D333" t="s">
+        <v>37</v>
+      </c>
+      <c r="E333">
+        <v>11228</v>
+      </c>
+      <c r="F333">
+        <v>2026</v>
+      </c>
+      <c r="G333" t="s">
+        <v>334</v>
+      </c>
+      <c r="H333" t="s">
+        <v>24</v>
+      </c>
+      <c r="K333" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L333" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M333" s="3" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A334" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C334" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D334" t="s">
+        <v>71</v>
+      </c>
+      <c r="E334">
+        <v>10471</v>
+      </c>
+      <c r="F334">
+        <v>2026</v>
+      </c>
+      <c r="G334" t="s">
+        <v>334</v>
+      </c>
+      <c r="H334" t="s">
+        <v>1229</v>
+      </c>
+      <c r="K334" t="s">
+        <v>1180</v>
+      </c>
+      <c r="L334" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M334" s="3" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A335" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C335" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D335" t="s">
+        <v>71</v>
+      </c>
+      <c r="E335">
+        <v>10463</v>
+      </c>
+      <c r="F335">
+        <v>2026</v>
+      </c>
+      <c r="G335" t="s">
+        <v>334</v>
+      </c>
+      <c r="H335" t="s">
+        <v>1229</v>
+      </c>
+      <c r="K335" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L335" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M335" s="3" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A336" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C336" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D336" t="s">
+        <v>37</v>
+      </c>
+      <c r="E336">
+        <v>11211</v>
+      </c>
+      <c r="F336">
+        <v>2026</v>
+      </c>
+      <c r="G336" t="s">
+        <v>334</v>
+      </c>
+      <c r="H336" t="s">
+        <v>104</v>
+      </c>
+      <c r="K336" t="s">
+        <v>1180</v>
+      </c>
+      <c r="L336" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M336" s="3" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="337" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A337" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C337" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D337" t="s">
+        <v>16</v>
+      </c>
+      <c r="E337">
+        <v>10301</v>
+      </c>
+      <c r="F337">
+        <v>2026</v>
+      </c>
+      <c r="G337" t="s">
+        <v>334</v>
+      </c>
+      <c r="H337" t="s">
+        <v>31</v>
+      </c>
+      <c r="K337" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L337" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M337" s="3" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="338" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A338" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C338" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D338" t="s">
+        <v>111</v>
+      </c>
+      <c r="E338">
+        <v>10044</v>
+      </c>
+      <c r="F338">
+        <v>2026</v>
+      </c>
+      <c r="G338" t="s">
+        <v>1240</v>
+      </c>
+      <c r="H338" t="s">
+        <v>1241</v>
+      </c>
+      <c r="K338" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L338" t="s">
+        <v>1196</v>
+      </c>
+      <c r="M338" s="3" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="339" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A339" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C339" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D339" t="s">
+        <v>111</v>
+      </c>
+      <c r="E339">
+        <v>10128</v>
+      </c>
+      <c r="F339">
+        <v>2026</v>
+      </c>
+      <c r="G339" t="s">
+        <v>334</v>
+      </c>
+      <c r="H339" t="s">
+        <v>1241</v>
+      </c>
+      <c r="K339" t="s">
+        <v>1180</v>
+      </c>
+      <c r="L339" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M339" s="3" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="340" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A340" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C340" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D340" t="s">
+        <v>16</v>
+      </c>
+      <c r="E340">
+        <v>10312</v>
+      </c>
+      <c r="F340">
+        <v>2026</v>
+      </c>
+      <c r="G340" t="s">
+        <v>334</v>
+      </c>
+      <c r="H340" t="s">
+        <v>335</v>
+      </c>
+      <c r="K340" t="s">
+        <v>1180</v>
+      </c>
+      <c r="L340" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M340" s="3" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="341" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A341" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C341" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D341" t="s">
+        <v>37</v>
+      </c>
+      <c r="E341">
+        <v>11229</v>
+      </c>
+      <c r="F341">
+        <v>2026</v>
+      </c>
+      <c r="G341" t="s">
+        <v>334</v>
+      </c>
+      <c r="H341" t="s">
+        <v>1249</v>
+      </c>
+      <c r="K341" t="s">
+        <v>1180</v>
+      </c>
+      <c r="L341" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M341" s="3" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="342" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A342" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C342" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D342" t="s">
+        <v>37</v>
+      </c>
+      <c r="E342">
+        <v>11224</v>
+      </c>
+      <c r="F342">
+        <v>2026</v>
+      </c>
+      <c r="G342" t="s">
+        <v>334</v>
+      </c>
+      <c r="H342" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K342" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L342" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M342" s="3" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="343" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A343" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C343" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D343" t="s">
+        <v>37</v>
+      </c>
+      <c r="E343">
+        <v>11224</v>
+      </c>
+      <c r="F343">
+        <v>2026</v>
+      </c>
+      <c r="G343" t="s">
+        <v>334</v>
+      </c>
+      <c r="H343" t="s">
+        <v>38</v>
+      </c>
+      <c r="K343" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L343" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M343" s="3" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="344" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A344" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C344" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D344" t="s">
+        <v>37</v>
+      </c>
+      <c r="E344">
+        <v>11204</v>
+      </c>
+      <c r="F344">
+        <v>2026</v>
+      </c>
+      <c r="G344" t="s">
+        <v>334</v>
+      </c>
+      <c r="H344" t="s">
+        <v>1259</v>
+      </c>
+      <c r="K344" t="s">
+        <v>1180</v>
+      </c>
+      <c r="L344" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M344" s="3" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="345" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A345" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C345" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D345" t="s">
+        <v>111</v>
+      </c>
+      <c r="E345">
+        <v>10036</v>
+      </c>
+      <c r="F345">
+        <v>2026</v>
+      </c>
+      <c r="G345" t="s">
+        <v>334</v>
+      </c>
+      <c r="H345" t="s">
+        <v>1262</v>
+      </c>
+      <c r="K345" t="s">
+        <v>1181</v>
+      </c>
+      <c r="L345" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M345" s="3" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="346" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A346" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C346" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D346" t="s">
+        <v>111</v>
+      </c>
+      <c r="E346">
+        <v>10011</v>
+      </c>
+      <c r="F346">
+        <v>2026</v>
+      </c>
+      <c r="G346" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H346" t="s">
+        <v>1266</v>
+      </c>
+      <c r="K346" t="s">
+        <v>1182</v>
+      </c>
+      <c r="L346" t="s">
+        <v>1196</v>
+      </c>
+      <c r="N346" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="O346" s="3" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="347" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A347" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C347" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D347" t="s">
+        <v>111</v>
+      </c>
+      <c r="E347">
+        <v>10003</v>
+      </c>
+      <c r="F347">
+        <v>2026</v>
+      </c>
+      <c r="G347" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H347" t="s">
+        <v>1266</v>
+      </c>
+      <c r="K347" t="s">
+        <v>1182</v>
+      </c>
+      <c r="L347" t="s">
+        <v>1196</v>
+      </c>
+      <c r="N347" s="3" t="s">
+        <v>1298</v>
+      </c>
+      <c r="O347" s="3" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="348" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A348" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C348" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D348" t="s">
+        <v>111</v>
+      </c>
+      <c r="E348">
+        <v>10028</v>
+      </c>
+      <c r="F348">
+        <v>2026</v>
+      </c>
+      <c r="G348" t="s">
+        <v>1271</v>
+      </c>
+      <c r="H348" t="s">
+        <v>1262</v>
+      </c>
+      <c r="K348" t="s">
+        <v>1182</v>
+      </c>
+      <c r="L348" t="s">
+        <v>1196</v>
+      </c>
+      <c r="N348" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="O348" s="3" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="349" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A349" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C349" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D349" t="s">
+        <v>11</v>
+      </c>
+      <c r="E349">
+        <v>11105</v>
+      </c>
+      <c r="F349">
+        <v>2026</v>
+      </c>
+      <c r="G349" t="s">
+        <v>503</v>
+      </c>
+      <c r="H349" t="s">
+        <v>149</v>
+      </c>
+      <c r="K349" t="s">
+        <v>1182</v>
+      </c>
+      <c r="L349" t="s">
+        <v>1196</v>
+      </c>
+      <c r="N349" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="O349" s="3" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="350" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A350" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C350" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D350" t="s">
+        <v>16</v>
+      </c>
+      <c r="E350">
+        <v>10304</v>
+      </c>
+      <c r="F350">
+        <v>2026</v>
+      </c>
+      <c r="G350" t="s">
+        <v>472</v>
+      </c>
+      <c r="H350" t="s">
+        <v>24</v>
+      </c>
+      <c r="K350" t="s">
+        <v>1182</v>
+      </c>
+      <c r="L350" t="s">
+        <v>1196</v>
+      </c>
+      <c r="N350" s="3" t="s">
+        <v>1304</v>
+      </c>
+      <c r="O350" s="3" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="351" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A351" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C351" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D351" t="s">
+        <v>37</v>
+      </c>
+      <c r="E351">
+        <v>11209</v>
+      </c>
+      <c r="F351">
+        <v>2026</v>
+      </c>
+      <c r="G351" t="s">
+        <v>334</v>
+      </c>
+      <c r="H351" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K351" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L351" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M351" s="3" t="s">
+        <v>1280</v>
       </c>
     </row>
   </sheetData>

--- a/data/total_edits.xlsx
+++ b/data/total_edits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/LLopez-Jensen/Documents/GitHub/9-11-memorials/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59AEA47E-0E39-C34D-9F9B-6449225BD071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAA754D-457D-5242-8B08-FE92820AE1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40800" yWindow="1360" windowWidth="38400" windowHeight="19180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38400" yWindow="620" windowWidth="38400" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2502" uniqueCount="1307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2528" uniqueCount="1333">
   <si>
     <t>new_name</t>
   </si>
@@ -4084,6 +4084,126 @@
   </si>
   <si>
     <t>POINT (-73.94477273249007 40.77495533249186)</t>
+  </si>
+  <si>
+    <t>The Firemen’s Memorial in Riverside Park dates to 1913, and includes a grand staircase, a plaza, a fountain basin, and the central marble monument. It has long been a place of remembrance for firefighters who lost their lives in the line of duty, but after 9/11 it also became a place of gathering for vigils and annual remembrance ceremonies for the firefighters who were killed at the World Trade Center that day. Each year, a ceremony is held at the memorial with hundreds of U.S. flags arrayed around it honoring firefighters who were killed that day and the hundreds more that have died of 9/11 related illness since. </t>
+  </si>
+  <si>
+    <t>Along 85th Street, between 157th Ave and Shore Parkway in Queens, there are a number of 9/11 remembrances. A 9/11 tribute mural created by local artists and volunteers was unveiled in 2021 at a ‘Remembering September 11th’ ceremony below an overpass on the border between Howard Beach and Lindenwood. Howard Beach is home to many first responders, people who worked at Ground Zero in the months following the attacks and survivors of that tragic day. In 2022, just down the block, a Callery pear tree sapling from the original 9/11 survivor tree was planted in Howard Beach on the grounds of the former Rockwood Jewish Center. Annual remembrance events occur along this stretch, and within the nearby Our Lady of Grace, with very active community participation.   </t>
+  </si>
+  <si>
+    <t>On September 11, 2001, the space at the corner of Beach Channel Drive and Beach 116th Street, facing Jamaica Bay, and thus the Twin Towers, was an undeveloped lot. The Rockaway Chamber of Commerce and the Friends of Tribute Park Committee worked to designate the space as a tribute park, which then occurred in 2005. The garden was designed by Lynden Miller and its pavilion by Patrick Clark. The park contains a mosaic centerpiece, a path of memorial bricks, and a granite rock with the engraved names of all 343 firefighters who lost their lives on September 11th. Annual remembrances, where 9/11 families place roses, have been held at the park.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Tunnel to Towers 5K Run &amp; Walk NYC is a tribute to the 343 FDNY firefighters, law enforcement officers, and thousands of civilians whose lives were lost on 9/11, those still affected by 9/11-related illnesses, and the service members who subsequently gave their lives. Participants retrace the final footsteps of FDNY Firefighter Stephen Siller, who on September 11, 2001 ran through the Brooklyn-Battery Tunnel carrying 60 pounds of fire gear to get to Ground Zero where he laid down his life to save others. The route begins in Brooklyn, at the intersection of Hamilton Avenue and Bowne Street, proceeds through the Hugh L. Carey Tunnel, and ends on West Street in Manhattan.   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A stone memorial in St. Michael’s Cemetery in Queens is dedicated to 76 Queens Firefighters whose lives were lost on September 11th. Alongside an image of a firefighter and the Twin Towers, is inscribed the names of the firefighters and the words: “The gift you gave, the price you paid will never be forgotten, as surely as your life you gave, our gratitude is written; Inscribed today on history's page for all the world to see, a lore of one who modeled courage, a hero's legacy.” St. Michael's Cemetery has held memorial service remembrances for those whose lives were lost on 9/11, as well as a "Remember Me" Run/Walk through the peaceful grounds of the cemetery, in their memory.  </t>
+  </si>
+  <si>
+    <t>Angels Circle is a memorial to the victims of September 11th who were from Staten Island. There are rows of more than 200 pictures of victims, each on a stand with their name and birthday displayed and memorabilia left by friends and family below their picture. Previously an empty lot, Wendy Pellegrino started the memorial on the night of the September 11th attacks by placing two candles and a handmade sign that read “God Bless America.” In the following days, mourners began placing pictures of their loved ones that did not return home on popsicle sticks next to the candles.  An annual vigil is held at the site on September 10th so families can go to Ground Zero on the anniversary of 9/11.</t>
+  </si>
+  <si>
+    <t>On the grounds of Monsignor Farrell High School, a 9/11 memorial wall was designed, built, and donated by an alumni of the school, Brian Hall. The monument lists the names of school alumni, and friends of the school, who lost their lives on 9/11. A remembrance mass is held by the school annually.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Poly Prep community constructed a memorial garden opposite the pond at the front of the school as a tribute to alumni who lost their lives on 9/11. The memorial garden featured a plaque, a sundial, and a small garden, and was detailed in the documentary “Lessons of September: One School Remembers 9/11.” Annually, students and staff would convene in the memorial garden, and 11 students who were 9/11 Memorial Scholars were selected to participate. In 2022, Poly Prep switched from the traditional gatherings to classroom discussions for students, although small ceremonies have remained.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endor Garden is a small, wooded area near West 253rd Street and Fieldston Road. This community garden, which now contains the memorial, was being created by Hilary Kitasei, and neighbors whom she had organized, when September 11th occurred and was completed soon after. The name Endor was given to the garden by Hilary’s daughters. Shortly after the attacks, contractor Jerry Fontan created and erected a wooden plaque dedicating the garden to those lost on 9/11 and which included the names of five firefighters and police officers who were from the area. In 2017, the plaque was vandalized. On the 20th anniversary of the attacks on the World Trade Center, a replacement plaque, created by the students and staff of Riverdale Country School, was erected. Funding for the new sign was raised by through the school’s student council annual dance-a-thon. On the new plaque, they included the names of five area firefighters and police officers who lost their lives on September 11th and expanded it to include those who lost their lives to 9/11 related illnesses. A remembrance ceremony is held annually. </t>
+  </si>
+  <si>
+    <t>The Lehman College campus holds an annual remembrance event to honor members of its community, including three alumni and one then-student, who lost their lives on September 11th.</t>
+  </si>
+  <si>
+    <t>At the corner of Conselyea Street and Graham Avenue in Brooklyn, a September 11th monument which contains the names of eight area residents who were killed at the World Trade Center. It has served as a focal point of remembrance in the community, including for the organizing of a prayer service by the Knights of Columbus.</t>
+  </si>
+  <si>
+    <t>“Postcards” features two soaring 40-foot high, white wing-like walls that symbolize notes sent to loved ones. The memorial is dedicated to all the Staten Island residents whose lives were lost on September 11th, each of them honored with a granite plaque with their facial silhouette, name, birth date, and place of work. Ground Zero can be seen between the “Postcards” wings. The memorial was designed by New York-based architect Masayuki Sono, who won the design competition held in early 2003, and it was opened on September 11, 2004. A survivor tree was later added to the memorial. Adjacent is a separate memorial to 73 Staten Island first responders who have died in recent years from exposure to toxic substances at the World Trade Center site in the aftermath of September 11th. The ‘Friends of Postcards’ have regularly held a public remembrance ceremony at the site.</t>
+  </si>
+  <si>
+    <t>A memorial plaque and remembrance tree honor the Roosevelt Islanders whose lives were lost on September 11th, and from illness in the following years, at Good Shepherd Plaza. An annual Roosevelt Island Operating Corporation 9/11 Remembrance Ceremony has been held at the site.</t>
+  </si>
+  <si>
+    <t>The Upper East Side Community Unity Initiative holds an annual East Side 9/11 Remembrance ceremony in Carl Schurz Park. The ceremony includes music, poetry and personal reflections from community members and special guests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh Kills served as a significant September 11th recovery location for sorting debris and where over 4,000 human remains were recovered. About 1.4 million tons of material was brought to Fresh Kills, with 500 barges loaded by DSNY and a further 1,500 barges laded by Weeks Marine, each containing 600 tons of material, and sorted by forensics, in some cases so finely that the material passed through a ¼ inch sieve. The barges landed on the west side of the park. After screening and sifting, the remaining World Trade Center material was placed in a 48-acre area in Section 1/9 at Freshkills, a 225ft. mound at the western boundary of the park. To prevent any type of disturbance of the material, a one-foot layer of non-toxic, contaminant-free soil was placed on the land below the materials prior to placement of the screened materials. After the sorting process was complete, the area was covered with additional healthy soil to control erosion and protect the site. DSNY’s exhaustive recovery efforts ensured materials were handled with care. Material from the World Trade Center site was transferred to Section 1/9 until July 15, 2002, and the final items were sorted and screened on July 26th of that same year. Throughout the entire process, DSNY’s core mission was to move all the material to the site and sort through it with the utmost care and respect. This 24/7, 10-month recovery effort took place without disrupting normal DSNY operations in the city.   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">An annual memorial ceremony, with speeches, music, and candles, is held near the flagpole next to Marine Park’s Carmine Carro Center. It is sponsored by local not-for-profits and is well attended, including by families of those lost and first responders. Even many years after 9/11, crowds at the event have numbered in the hundreds. </t>
+  </si>
+  <si>
+    <t>The Brooklyn Wall of Remembrance allows visitors to remember and honor the brave responders who selflessly gave their lives to save others on September 11th. The wall is comprised of three 30 x 12-foot granite walls, laser-engraved with images of the 346 firefighters, 37 Port Authority officers, 23 NYC police officers, 3 NYS officers, 1 fire patrol, first responders, and Sirius, a K-9 rescue dog who tragically lost their lives that day. An annual candlelight ceremony, called ‘A Light and a Prayer,’ has been held at the Brooklyn Wall, and the foundation supporting the wall has been involved in many other community buildings endeavors, including a Hero Dog Program and annual Heroes Night with the Brooklyn Cyclones.</t>
+  </si>
+  <si>
+    <t>In 2002, at Asser Levy Park in Brooklyn, a group of individuals came together to plant a whipping willow tree, and they went on to build a memorial square around that tree. The square, with plaques, seating, and plantings, was completed in 2005, and serves as a space for quiet reflection and remembrance of the impacts of September 11th on the local Russian-speaking community, and all peoples. A plaque reads “In Memorium to all those who perished in the terrorist attack of September 11, 2001. Individuals of different, ages, nationalities and religions, our sons and daughters, mothers and fathers, husband and wives, brothers and sisters, friends and relatives, who lost their lives on that tragic day.” Another plaque lists the names of 18 people who lost their lives on September 11th. The September 11 Family Group holds an annual public memorial ceremony at the site, where the community places flowers and light candles in tribute.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 9/11 memorial service has been held at Seth Low Park which includes prayers from religious leaders of various faiths, and speakers recalling the horrific events that took place on September 11th. In addition, students from the Seth Low Intermediate School perform the National Anthem and lead the Pledge of Allegiance.   </t>
+  </si>
+  <si>
+    <t>The Marsh &amp; McLennan September 11th Memorial is a quiet, reflective public garden located in Midtown Manhattan behind the company's former headquarters at 1166 Avenue of the Americas. Dedicated in 2004, it honors the 358 company employees and consultants who lost their lives in the World Trade Center. A remembrance event is held annually, and a website is maintained with general tributes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On the morning of September 11, 2001, Squad 18 deployed from its Greenwich Village/West Village firehouse in Manhattan to the Twin Towers. Members of the unit engaged in rescue and emergency operations, including using rope to secure trapped window washers. FDNY Squad 18 lost seven firefighters during the September 11 terrorist attacks. Names of the members who were killed include:  
+Capt. William E McGinn 
+FF Eric T Allen 
+Lt. Andrew A Fredericks  
+Lt. David Halderman  
+FF Timothy S Haskell 
+FF Manuel D Mojica Jr. 
+FF Lawrence J Virgilio </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Led by Captain Patrick “Paddy” John Brown, the East Village unit arrived at the WTC minutes after the first plane hit. When the North Tower collapsed all 11 responding members of Ladder 3 perished inside. Their heavily mangled and crushed fire truck was recovered and is now preserved as a permanent exhibit at the National September 11 Memorial &amp; Museum. Names of the members who were killed include: 
+Captain Patrick J Brown 
+Lt. Kevin W Donnelly 
+FF Michael T Carroll 
+FF James R Coyle 
+FF Gerard P Dewan 
+FF Jeffrey J Giordano 
+FF Michael H Haub 
+FF William J Mahoney 
+FF Timothy P McSweeney 
+FF Joseph E Maloney 
+FF Leonard J Ragaglia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lost nine firefighters during the September 11th attacks, becoming known as the "Yorkville 9". Four members from Engine 22 and five members from Ladder 13 lost their lives at the WTC. Names of the members who were killed include:  
+Engine 22 
+FF Thomas A Casoria 
+FF Michael J Elferis 
+Fire Marshal Vincent D Kane 
+FF Martin E McWilliams  
+Ladder 13 
+Captain Walter G Hynes 
+FF Thomas J Hetzel 
+FF Dennis P McHugh 
+FF Thomas E Sabella 
+FF Gregory M Stajk </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paramedic Carlos Lillo was a 37-year-old FDNY paramedic assigned to EMS Battalion 49. On September 11, 2001, he rushed to the scene and was actively treating evacuees in a triage area. He was last seen running into the World Trade Center concourse near the South Tower lobby to assist a patient in cardiac arrest right before the tower collapsed.   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On September 11th, Rescue 5 arrived at the WTC to assist with fighting fires and rescuing people from the Twin Towers. Rescue 5 lost all 11 firefighters, the most of any single fire station throughout the City that day. Names of the members who were killed include:
+Battalion Chief Louis J. Modafferi 
+Lt. Harvey L Harrell 
+Lt. Michael T Russo 
+Lt. Joseph A Mascali 
+Lt. Charles J Margiotta 
+FF Carl V Bini 
+FF Michael C Fiore 
+FF John P Bergin 
+FF Allan Tarasiewicz 
+FF Douglas C Miller 
+FF Nicholas P Rossomando 
+FF Jeffrey A Palazzo 
+Fire Marshal Andre G Fletcher </t>
+  </si>
+  <si>
+    <t>On American Veterans Memorial Pier, also known as the 69th Street Pier, is the September 11 Beacon memorial. It was designed and built by artist Robert Ressler, after being selected through a competition. The memorial, in the symbolic shape of a speaking trumpet once used by volunteer fire brigades, was cast from bronze at Bedi-Macky, a foundry in Greenpoint, and features a beacon of light shining from the top that is illuminated annually on September 11th. Annual vigils, often with performances by local school bands, such as nearby Xaverian High School, and ceremonials by scout troops, have been held on the pier, alongside the memorial.</t>
   </si>
 </sst>
 </file>
@@ -4134,7 +4254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4143,6 +4263,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4158,10 +4279,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13623,6 +13740,9 @@
       <c r="A326" t="s">
         <v>1208</v>
       </c>
+      <c r="B326" t="s">
+        <v>1307</v>
+      </c>
       <c r="C326" t="s">
         <v>1209</v>
       </c>
@@ -13655,6 +13775,9 @@
       <c r="A327" t="s">
         <v>1212</v>
       </c>
+      <c r="B327" t="s">
+        <v>1308</v>
+      </c>
       <c r="C327" t="s">
         <v>1213</v>
       </c>
@@ -13687,6 +13810,9 @@
       <c r="A328" t="s">
         <v>1214</v>
       </c>
+      <c r="B328" t="s">
+        <v>1309</v>
+      </c>
       <c r="C328" t="s">
         <v>1215</v>
       </c>
@@ -13719,6 +13845,9 @@
       <c r="A329" t="s">
         <v>1216</v>
       </c>
+      <c r="B329" t="s">
+        <v>1310</v>
+      </c>
       <c r="C329" t="s">
         <v>1217</v>
       </c>
@@ -13751,6 +13880,9 @@
       <c r="A330" t="s">
         <v>1219</v>
       </c>
+      <c r="B330" t="s">
+        <v>1311</v>
+      </c>
       <c r="C330" t="s">
         <v>1220</v>
       </c>
@@ -13783,6 +13915,9 @@
       <c r="A331" t="s">
         <v>1221</v>
       </c>
+      <c r="B331" t="s">
+        <v>1312</v>
+      </c>
       <c r="C331" t="s">
         <v>1222</v>
       </c>
@@ -13815,6 +13950,9 @@
       <c r="A332" t="s">
         <v>1223</v>
       </c>
+      <c r="B332" t="s">
+        <v>1313</v>
+      </c>
       <c r="C332" t="s">
         <v>1224</v>
       </c>
@@ -13847,6 +13985,9 @@
       <c r="A333" t="s">
         <v>1225</v>
       </c>
+      <c r="B333" t="s">
+        <v>1314</v>
+      </c>
       <c r="C333" t="s">
         <v>1226</v>
       </c>
@@ -13879,6 +14020,9 @@
       <c r="A334" t="s">
         <v>1227</v>
       </c>
+      <c r="B334" t="s">
+        <v>1315</v>
+      </c>
       <c r="C334" t="s">
         <v>1228</v>
       </c>
@@ -13911,6 +14055,9 @@
       <c r="A335" t="s">
         <v>1230</v>
       </c>
+      <c r="B335" t="s">
+        <v>1316</v>
+      </c>
       <c r="C335" t="s">
         <v>1231</v>
       </c>
@@ -13943,6 +14090,9 @@
       <c r="A336" t="s">
         <v>1232</v>
       </c>
+      <c r="B336" t="s">
+        <v>1317</v>
+      </c>
       <c r="C336" t="s">
         <v>1233</v>
       </c>
@@ -13962,7 +14112,7 @@
         <v>104</v>
       </c>
       <c r="K336" t="s">
-        <v>1180</v>
+        <v>1001</v>
       </c>
       <c r="L336" t="s">
         <v>1197</v>
@@ -13975,6 +14125,9 @@
       <c r="A337" t="s">
         <v>1235</v>
       </c>
+      <c r="B337" t="s">
+        <v>1318</v>
+      </c>
       <c r="C337" t="s">
         <v>1236</v>
       </c>
@@ -14007,6 +14160,9 @@
       <c r="A338" t="s">
         <v>1238</v>
       </c>
+      <c r="B338" t="s">
+        <v>1319</v>
+      </c>
       <c r="C338" t="s">
         <v>1239</v>
       </c>
@@ -14039,6 +14195,9 @@
       <c r="A339" t="s">
         <v>1243</v>
       </c>
+      <c r="B339" t="s">
+        <v>1320</v>
+      </c>
       <c r="C339" t="s">
         <v>1244</v>
       </c>
@@ -14071,6 +14230,9 @@
       <c r="A340" t="s">
         <v>1245</v>
       </c>
+      <c r="B340" t="s">
+        <v>1321</v>
+      </c>
       <c r="C340" t="s">
         <v>1246</v>
       </c>
@@ -14103,6 +14265,9 @@
       <c r="A341" t="s">
         <v>1247</v>
       </c>
+      <c r="B341" t="s">
+        <v>1322</v>
+      </c>
       <c r="C341" t="s">
         <v>1248</v>
       </c>
@@ -14135,6 +14300,9 @@
       <c r="A342" t="s">
         <v>1251</v>
       </c>
+      <c r="B342" t="s">
+        <v>1323</v>
+      </c>
       <c r="C342" t="s">
         <v>1252</v>
       </c>
@@ -14167,6 +14335,9 @@
       <c r="A343" t="s">
         <v>1254</v>
       </c>
+      <c r="B343" t="s">
+        <v>1324</v>
+      </c>
       <c r="C343" t="s">
         <v>1255</v>
       </c>
@@ -14199,6 +14370,9 @@
       <c r="A344" t="s">
         <v>1257</v>
       </c>
+      <c r="B344" t="s">
+        <v>1325</v>
+      </c>
       <c r="C344" t="s">
         <v>1258</v>
       </c>
@@ -14231,6 +14405,9 @@
       <c r="A345" t="s">
         <v>1260</v>
       </c>
+      <c r="B345" t="s">
+        <v>1326</v>
+      </c>
       <c r="C345" t="s">
         <v>1261</v>
       </c>
@@ -14263,6 +14440,9 @@
       <c r="A346" t="s">
         <v>1264</v>
       </c>
+      <c r="B346" s="4" t="s">
+        <v>1327</v>
+      </c>
       <c r="C346" t="s">
         <v>1265</v>
       </c>
@@ -14298,6 +14478,9 @@
       <c r="A347" t="s">
         <v>1267</v>
       </c>
+      <c r="B347" s="4" t="s">
+        <v>1328</v>
+      </c>
       <c r="C347" t="s">
         <v>1268</v>
       </c>
@@ -14333,6 +14516,9 @@
       <c r="A348" t="s">
         <v>1269</v>
       </c>
+      <c r="B348" s="4" t="s">
+        <v>1329</v>
+      </c>
       <c r="C348" t="s">
         <v>1270</v>
       </c>
@@ -14368,6 +14554,9 @@
       <c r="A349" t="s">
         <v>1274</v>
       </c>
+      <c r="B349" s="4" t="s">
+        <v>1330</v>
+      </c>
       <c r="C349" t="s">
         <v>1275</v>
       </c>
@@ -14403,6 +14592,9 @@
       <c r="A350" t="s">
         <v>1276</v>
       </c>
+      <c r="B350" s="4" t="s">
+        <v>1331</v>
+      </c>
       <c r="C350" t="s">
         <v>1277</v>
       </c>
@@ -14419,7 +14611,7 @@
         <v>472</v>
       </c>
       <c r="H350" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K350" t="s">
         <v>1182</v>
@@ -14437,6 +14629,9 @@
     <row r="351" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>1278</v>
+      </c>
+      <c r="B351" s="4" t="s">
+        <v>1332</v>
       </c>
       <c r="C351" t="s">
         <v>1279</v>

--- a/data/total_edits.xlsx
+++ b/data/total_edits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/LLopez-Jensen/Documents/GitHub/9-11-memorials/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAA754D-457D-5242-8B08-FE92820AE1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836BB2EF-17C4-1E4C-9BB3-3283B3988D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38400" yWindow="620" windowWidth="38400" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4089,9 +4089,6 @@
     <t>The Firemen’s Memorial in Riverside Park dates to 1913, and includes a grand staircase, a plaza, a fountain basin, and the central marble monument. It has long been a place of remembrance for firefighters who lost their lives in the line of duty, but after 9/11 it also became a place of gathering for vigils and annual remembrance ceremonies for the firefighters who were killed at the World Trade Center that day. Each year, a ceremony is held at the memorial with hundreds of U.S. flags arrayed around it honoring firefighters who were killed that day and the hundreds more that have died of 9/11 related illness since. </t>
   </si>
   <si>
-    <t>Along 85th Street, between 157th Ave and Shore Parkway in Queens, there are a number of 9/11 remembrances. A 9/11 tribute mural created by local artists and volunteers was unveiled in 2021 at a ‘Remembering September 11th’ ceremony below an overpass on the border between Howard Beach and Lindenwood. Howard Beach is home to many first responders, people who worked at Ground Zero in the months following the attacks and survivors of that tragic day. In 2022, just down the block, a Callery pear tree sapling from the original 9/11 survivor tree was planted in Howard Beach on the grounds of the former Rockwood Jewish Center. Annual remembrance events occur along this stretch, and within the nearby Our Lady of Grace, with very active community participation.   </t>
-  </si>
-  <si>
     <t>On September 11, 2001, the space at the corner of Beach Channel Drive and Beach 116th Street, facing Jamaica Bay, and thus the Twin Towers, was an undeveloped lot. The Rockaway Chamber of Commerce and the Friends of Tribute Park Committee worked to designate the space as a tribute park, which then occurred in 2005. The garden was designed by Lynden Miller and its pavilion by Patrick Clark. The park contains a mosaic centerpiece, a path of memorial bricks, and a granite rock with the engraved names of all 343 firefighters who lost their lives on September 11th. Annual remembrances, where 9/11 families place roses, have been held at the park.</t>
   </si>
   <si>
@@ -4204,6 +4201,9 @@
   </si>
   <si>
     <t>On American Veterans Memorial Pier, also known as the 69th Street Pier, is the September 11 Beacon memorial. It was designed and built by artist Robert Ressler, after being selected through a competition. The memorial, in the symbolic shape of a speaking trumpet once used by volunteer fire brigades, was cast from bronze at Bedi-Macky, a foundry in Greenpoint, and features a beacon of light shining from the top that is illuminated annually on September 11th. Annual vigils, often with performances by local school bands, such as nearby Xaverian High School, and ceremonials by scout troops, have been held on the pier, alongside the memorial.</t>
+  </si>
+  <si>
+    <t>Along 84th Street, between 157th Ave and Shore Parkway in Queens, there are a number of 9/11 remembrances. A 9/11 tribute mural created by local artists and volunteers was unveiled in 2021 at a ‘Remembering September 11th’ ceremony below an overpass on the border between Howard Beach and Lindenwood. Howard Beach is home to many first responders, people who worked at Ground Zero in the months following the attacks and survivors of that tragic day. In 2022, just down the block, a Callery pear tree sapling from the original 9/11 survivor tree was planted in Howard Beach on the grounds of the former Rockwood Jewish Center. Annual remembrance events occur along this stretch, and within the nearby Our Lady of Grace, with very active community participation.   </t>
   </si>
 </sst>
 </file>
@@ -4254,7 +4254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4263,7 +4263,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13776,7 +13775,7 @@
         <v>1212</v>
       </c>
       <c r="B327" t="s">
-        <v>1308</v>
+        <v>1332</v>
       </c>
       <c r="C327" t="s">
         <v>1213</v>
@@ -13811,7 +13810,7 @@
         <v>1214</v>
       </c>
       <c r="B328" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="C328" t="s">
         <v>1215</v>
@@ -13846,7 +13845,7 @@
         <v>1216</v>
       </c>
       <c r="B329" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C329" t="s">
         <v>1217</v>
@@ -13881,7 +13880,7 @@
         <v>1219</v>
       </c>
       <c r="B330" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C330" t="s">
         <v>1220</v>
@@ -13916,7 +13915,7 @@
         <v>1221</v>
       </c>
       <c r="B331" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C331" t="s">
         <v>1222</v>
@@ -13951,7 +13950,7 @@
         <v>1223</v>
       </c>
       <c r="B332" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="C332" t="s">
         <v>1224</v>
@@ -13986,7 +13985,7 @@
         <v>1225</v>
       </c>
       <c r="B333" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C333" t="s">
         <v>1226</v>
@@ -14021,7 +14020,7 @@
         <v>1227</v>
       </c>
       <c r="B334" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C334" t="s">
         <v>1228</v>
@@ -14056,7 +14055,7 @@
         <v>1230</v>
       </c>
       <c r="B335" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="C335" t="s">
         <v>1231</v>
@@ -14091,7 +14090,7 @@
         <v>1232</v>
       </c>
       <c r="B336" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="C336" t="s">
         <v>1233</v>
@@ -14126,7 +14125,7 @@
         <v>1235</v>
       </c>
       <c r="B337" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C337" t="s">
         <v>1236</v>
@@ -14161,7 +14160,7 @@
         <v>1238</v>
       </c>
       <c r="B338" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C338" t="s">
         <v>1239</v>
@@ -14196,7 +14195,7 @@
         <v>1243</v>
       </c>
       <c r="B339" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C339" t="s">
         <v>1244</v>
@@ -14231,7 +14230,7 @@
         <v>1245</v>
       </c>
       <c r="B340" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C340" t="s">
         <v>1246</v>
@@ -14266,7 +14265,7 @@
         <v>1247</v>
       </c>
       <c r="B341" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="C341" t="s">
         <v>1248</v>
@@ -14301,7 +14300,7 @@
         <v>1251</v>
       </c>
       <c r="B342" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="C342" t="s">
         <v>1252</v>
@@ -14336,7 +14335,7 @@
         <v>1254</v>
       </c>
       <c r="B343" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="C343" t="s">
         <v>1255</v>
@@ -14371,7 +14370,7 @@
         <v>1257</v>
       </c>
       <c r="B344" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="C344" t="s">
         <v>1258</v>
@@ -14406,7 +14405,7 @@
         <v>1260</v>
       </c>
       <c r="B345" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C345" t="s">
         <v>1261</v>
@@ -14440,8 +14439,8 @@
       <c r="A346" t="s">
         <v>1264</v>
       </c>
-      <c r="B346" s="4" t="s">
-        <v>1327</v>
+      <c r="B346" t="s">
+        <v>1326</v>
       </c>
       <c r="C346" t="s">
         <v>1265</v>
@@ -14478,8 +14477,8 @@
       <c r="A347" t="s">
         <v>1267</v>
       </c>
-      <c r="B347" s="4" t="s">
-        <v>1328</v>
+      <c r="B347" t="s">
+        <v>1327</v>
       </c>
       <c r="C347" t="s">
         <v>1268</v>
@@ -14516,8 +14515,8 @@
       <c r="A348" t="s">
         <v>1269</v>
       </c>
-      <c r="B348" s="4" t="s">
-        <v>1329</v>
+      <c r="B348" t="s">
+        <v>1328</v>
       </c>
       <c r="C348" t="s">
         <v>1270</v>
@@ -14554,8 +14553,8 @@
       <c r="A349" t="s">
         <v>1274</v>
       </c>
-      <c r="B349" s="4" t="s">
-        <v>1330</v>
+      <c r="B349" t="s">
+        <v>1329</v>
       </c>
       <c r="C349" t="s">
         <v>1275</v>
@@ -14592,8 +14591,8 @@
       <c r="A350" t="s">
         <v>1276</v>
       </c>
-      <c r="B350" s="4" t="s">
-        <v>1331</v>
+      <c r="B350" t="s">
+        <v>1330</v>
       </c>
       <c r="C350" t="s">
         <v>1277</v>
@@ -14630,8 +14629,8 @@
       <c r="A351" t="s">
         <v>1278</v>
       </c>
-      <c r="B351" s="4" t="s">
-        <v>1332</v>
+      <c r="B351" t="s">
+        <v>1331</v>
       </c>
       <c r="C351" t="s">
         <v>1279</v>
